--- a/New_Code/mutation.xlsx
+++ b/New_Code/mutation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B73E785-715C-483D-BA76-747EB8358DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6754C989-4E36-400E-89A6-753547E7B93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{25DD2874-44EC-4C00-8F62-207BA1D39B57}"/>
+    <workbookView xWindow="15810" yWindow="1485" windowWidth="12000" windowHeight="11295" xr2:uid="{25DD2874-44EC-4C00-8F62-207BA1D39B57}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Y248T</t>
-  </si>
-  <si>
-    <t>A123G</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>critère1</t>
   </si>
@@ -59,7 +53,16 @@
     <t>AA_important en contact</t>
   </si>
   <si>
-    <t>P489R</t>
+    <t>clash</t>
+  </si>
+  <si>
+    <t>critère4</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>L839T</t>
   </si>
 </sst>
 </file>
@@ -411,46 +414,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5762739B-326A-4783-9A65-DF487FD1A3E8}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/New_Code/mutation.xlsx
+++ b/New_Code/mutation.xlsx
@@ -8,35 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6754C989-4E36-400E-89A6-753547E7B93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE7A5A8-C747-4DF7-9E76-96C09DC55EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15810" yWindow="1485" windowWidth="12000" windowHeight="11295" xr2:uid="{25DD2874-44EC-4C00-8F62-207BA1D39B57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>critère1</t>
   </si>
@@ -47,13 +31,10 @@
     <t>critère3</t>
   </si>
   <si>
-    <t>minimisation</t>
+    <t>clash</t>
   </si>
   <si>
-    <t>AA_important en contact</t>
-  </si>
-  <si>
-    <t>clash</t>
+    <t>minimisation</t>
   </si>
   <si>
     <t>critère4</t>
@@ -62,14 +43,14 @@
     <t>total</t>
   </si>
   <si>
-    <t>L839T</t>
+    <t>AA_important en contact</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,16 +58,322 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -94,15 +381,233 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="56">
+    <cellStyle name="20 % - Accent1 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="20 % - Accent2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="20 % - Accent3 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="20 % - Accent4 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="20 % - Accent5 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="20 % - Accent6 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="40 % - Accent1 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="40 % - Accent2 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="40 % - Accent3 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="40 % - Accent4 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="40 % - Accent5 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="40 % - Accent6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="60 % - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="60 % - Accent1 3" xfId="28" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="60 % - Accent1 4" xfId="50" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="60 % - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="60 % - Accent2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="60 % - Accent2 4" xfId="51" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="60 % - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="60 % - Accent3 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="60 % - Accent3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="60 % - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="60 % - Accent4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="60 % - Accent4 4" xfId="53" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="60 % - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="60 % - Accent5 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="60 % - Accent5 4" xfId="54" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="60 % - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="60 % - Accent6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="60 % - Accent6 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Accent1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Accent2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Accent3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Accent4 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Accent5 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Accent6 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Avertissement 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Calcul 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Cellule liée 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Entrée 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Insatisfaisant 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Neutre 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Neutre 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Neutre 4" xfId="49" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Satisfaisant 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Sortie 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Texte explicatif 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Titre 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Titre 1 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Titre 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Titre 3 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Titre 4 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Total 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Vérification 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -413,56 +918,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5762739B-326A-4783-9A65-DF487FD1A3E8}">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/New_Code/mutation.xlsx
+++ b/New_Code/mutation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE7A5A8-C747-4DF7-9E76-96C09DC55EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522CAF5F-2570-4497-88C7-62C6CA3C1DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,7 +489,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="56">
+  <cellStyleXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
@@ -546,12 +546,33 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="56">
+  <cellStyles count="77">
     <cellStyle name="20 % - Accent1 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="20 % - Accent2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
     <cellStyle name="20 % - Accent3 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
@@ -566,22 +587,40 @@
     <cellStyle name="40 % - Accent6 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
     <cellStyle name="60 % - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="60 % - Accent1 3" xfId="28" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="60 % - Accent1 4" xfId="50" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="60 % - Accent1 4" xfId="50" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="60 % - Accent1 5" xfId="57" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="60 % - Accent1 6" xfId="64" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="60 % - Accent1 7" xfId="71" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
     <cellStyle name="60 % - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="60 % - Accent2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="60 % - Accent2 4" xfId="51" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="60 % - Accent2 4" xfId="51" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="60 % - Accent2 5" xfId="58" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="60 % - Accent2 6" xfId="65" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="60 % - Accent2 7" xfId="72" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
     <cellStyle name="60 % - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="60 % - Accent3 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="60 % - Accent3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="60 % - Accent3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="60 % - Accent3 5" xfId="59" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="60 % - Accent3 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="60 % - Accent3 7" xfId="73" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
     <cellStyle name="60 % - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="60 % - Accent4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="60 % - Accent4 4" xfId="53" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="60 % - Accent4 4" xfId="53" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="60 % - Accent4 5" xfId="60" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="60 % - Accent4 6" xfId="67" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="60 % - Accent4 7" xfId="74" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
     <cellStyle name="60 % - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="60 % - Accent5 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="60 % - Accent5 4" xfId="54" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="60 % - Accent5 4" xfId="54" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="60 % - Accent5 5" xfId="61" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="60 % - Accent5 6" xfId="68" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="60 % - Accent5 7" xfId="75" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
     <cellStyle name="60 % - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="60 % - Accent6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="60 % - Accent6 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="60 % - Accent6 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="60 % - Accent6 5" xfId="62" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="60 % - Accent6 6" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="60 % - Accent6 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
     <cellStyle name="Accent1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Accent2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="Accent3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
@@ -595,7 +634,10 @@
     <cellStyle name="Insatisfaisant 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
     <cellStyle name="Neutre 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Neutre 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Neutre 4" xfId="49" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Neutre 4" xfId="49" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Neutre 5" xfId="56" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Neutre 6" xfId="63" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Neutre 7" xfId="70" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="Satisfaisant 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
@@ -926,6 +968,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">

--- a/New_Code/mutation.xlsx
+++ b/New_Code/mutation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522CAF5F-2570-4497-88C7-62C6CA3C1DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2CFCDA-FBE2-45A4-978B-99C2B6754E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -489,7 +489,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="77">
+  <cellStyleXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
@@ -567,12 +567,19 @@
     <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="77">
+  <cellStyles count="84">
     <cellStyle name="20 % - Accent1 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="20 % - Accent2 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
     <cellStyle name="20 % - Accent3 2" xfId="34" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
@@ -590,37 +597,43 @@
     <cellStyle name="60 % - Accent1 4" xfId="50" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
     <cellStyle name="60 % - Accent1 5" xfId="57" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
     <cellStyle name="60 % - Accent1 6" xfId="64" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="60 % - Accent1 7" xfId="71" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="60 % - Accent1 7" xfId="71" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="60 % - Accent1 8" xfId="78" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
     <cellStyle name="60 % - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="60 % - Accent2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="60 % - Accent2 4" xfId="51" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
     <cellStyle name="60 % - Accent2 5" xfId="58" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
     <cellStyle name="60 % - Accent2 6" xfId="65" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="60 % - Accent2 7" xfId="72" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="60 % - Accent2 7" xfId="72" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="60 % - Accent2 8" xfId="79" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
     <cellStyle name="60 % - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="60 % - Accent3 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="60 % - Accent3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
     <cellStyle name="60 % - Accent3 5" xfId="59" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="60 % - Accent3 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="60 % - Accent3 7" xfId="73" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="60 % - Accent3 7" xfId="73" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="60 % - Accent3 8" xfId="80" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
     <cellStyle name="60 % - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="60 % - Accent4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="60 % - Accent4 4" xfId="53" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
     <cellStyle name="60 % - Accent4 5" xfId="60" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
     <cellStyle name="60 % - Accent4 6" xfId="67" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="60 % - Accent4 7" xfId="74" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="60 % - Accent4 7" xfId="74" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="60 % - Accent4 8" xfId="81" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
     <cellStyle name="60 % - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="60 % - Accent5 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
     <cellStyle name="60 % - Accent5 4" xfId="54" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
     <cellStyle name="60 % - Accent5 5" xfId="61" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
     <cellStyle name="60 % - Accent5 6" xfId="68" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="60 % - Accent5 7" xfId="75" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="60 % - Accent5 7" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="60 % - Accent5 8" xfId="82" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
     <cellStyle name="60 % - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="60 % - Accent6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
     <cellStyle name="60 % - Accent6 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="60 % - Accent6 5" xfId="62" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
     <cellStyle name="60 % - Accent6 6" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="60 % - Accent6 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="60 % - Accent6 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="60 % - Accent6 8" xfId="83" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
     <cellStyle name="Accent1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Accent2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="Accent3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
@@ -637,7 +650,8 @@
     <cellStyle name="Neutre 4" xfId="49" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="Neutre 5" xfId="56" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Neutre 6" xfId="63" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="Neutre 7" xfId="70" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Neutre 7" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Neutre 8" xfId="77" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="Satisfaisant 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
@@ -961,52 +975,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:BR9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="D1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BR1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>

--- a/New_Code/mutation.xlsx
+++ b/New_Code/mutation.xlsx
@@ -1,26 +1,480 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2CFCDA-FBE2-45A4-978B-99C2B6754E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4452137E-F7B0-45AA-8AB3-E5B1C1FB9A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12045" yWindow="1575" windowWidth="12000" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="502">
+  <si>
+    <t>A9V</t>
+  </si>
+  <si>
+    <t>Q11P</t>
+  </si>
+  <si>
+    <t>T13N</t>
+  </si>
+  <si>
+    <t>L15R</t>
+  </si>
+  <si>
+    <t>D16A</t>
+  </si>
+  <si>
+    <t>K21Q</t>
+  </si>
+  <si>
+    <t>K21T</t>
+  </si>
+  <si>
+    <t>E23A</t>
+  </si>
+  <si>
+    <t>G24S</t>
+  </si>
+  <si>
+    <t>Q25H</t>
+  </si>
+  <si>
+    <t>I31T</t>
+  </si>
+  <si>
+    <t>R35W</t>
+  </si>
+  <si>
+    <t>C44F</t>
+  </si>
+  <si>
+    <t>N45K</t>
+  </si>
+  <si>
+    <t>C49R</t>
+  </si>
+  <si>
+    <t>C52Y</t>
+  </si>
+  <si>
+    <t>G53S</t>
+  </si>
+  <si>
+    <t>E58K</t>
+  </si>
+  <si>
+    <t>V59G</t>
+  </si>
+  <si>
+    <t>C64T</t>
+  </si>
+  <si>
+    <t>T65P</t>
+  </si>
+  <si>
+    <t>C66Y</t>
+  </si>
+  <si>
+    <t>F68C</t>
+  </si>
+  <si>
+    <t>F68L</t>
+  </si>
+  <si>
+    <t>P72L</t>
+  </si>
+  <si>
+    <t>A78G</t>
+  </si>
+  <si>
+    <t>A79T</t>
+  </si>
+  <si>
+    <t>Q81H</t>
+  </si>
+  <si>
+    <t>I82M</t>
+  </si>
+  <si>
+    <t>G88D</t>
+  </si>
+  <si>
+    <t>R92C</t>
+  </si>
+  <si>
+    <t>R92L</t>
+  </si>
+  <si>
+    <t>K93E</t>
+  </si>
+  <si>
+    <t>K93R</t>
+  </si>
+  <si>
+    <t>I96T</t>
+  </si>
+  <si>
+    <t>Y99C</t>
+  </si>
+  <si>
+    <t>K101Q</t>
+  </si>
+  <si>
+    <t>D102A</t>
+  </si>
+  <si>
+    <t>P114S</t>
+  </si>
+  <si>
+    <t>M124T</t>
+  </si>
+  <si>
+    <t>F129C</t>
+  </si>
+  <si>
+    <t>V131L</t>
+  </si>
+  <si>
+    <t>H402R</t>
+  </si>
+  <si>
+    <t>P405S</t>
+  </si>
+  <si>
+    <t>V409M</t>
+  </si>
+  <si>
+    <t>L413F</t>
+  </si>
+  <si>
+    <t>L413R</t>
+  </si>
+  <si>
+    <t>Y420C</t>
+  </si>
+  <si>
+    <t>T421M</t>
+  </si>
+  <si>
+    <t>A422T</t>
+  </si>
+  <si>
+    <t>Y427H</t>
+  </si>
+  <si>
+    <t>S428L</t>
+  </si>
+  <si>
+    <t>F463L</t>
+  </si>
+  <si>
+    <t>Y475C</t>
+  </si>
+  <si>
+    <t>V476I</t>
+  </si>
+  <si>
+    <t>V483I</t>
+  </si>
+  <si>
+    <t>A490T</t>
+  </si>
+  <si>
+    <t>Y493H</t>
+  </si>
+  <si>
+    <t>P507S</t>
+  </si>
+  <si>
+    <t>K525N</t>
+  </si>
+  <si>
+    <t>T526A</t>
+  </si>
+  <si>
+    <t>R528W</t>
+  </si>
+  <si>
+    <t>R528P</t>
+  </si>
+  <si>
+    <t>R531T</t>
+  </si>
+  <si>
+    <t>R534C</t>
+  </si>
+  <si>
+    <t>V535M</t>
+  </si>
+  <si>
+    <t>G546C</t>
+  </si>
+  <si>
+    <t>L552S</t>
+  </si>
+  <si>
+    <t>L553V</t>
+  </si>
+  <si>
+    <t>M554T</t>
+  </si>
+  <si>
+    <t>A561P</t>
+  </si>
+  <si>
+    <t>A561V</t>
+  </si>
+  <si>
+    <t>L564Q</t>
+  </si>
+  <si>
+    <t>L564P</t>
+  </si>
+  <si>
+    <t>A565S</t>
+  </si>
+  <si>
+    <t>C566S</t>
+  </si>
+  <si>
+    <t>I567T</t>
+  </si>
+  <si>
+    <t>W568L</t>
+  </si>
+  <si>
+    <t>W568C</t>
+  </si>
+  <si>
+    <t>Y569C</t>
+  </si>
+  <si>
+    <t>A570T</t>
+  </si>
+  <si>
+    <t>E575G</t>
+  </si>
+  <si>
+    <t>Q576H</t>
+  </si>
+  <si>
+    <t>I583V</t>
+  </si>
+  <si>
+    <t>I583M</t>
+  </si>
+  <si>
+    <t>G584S</t>
+  </si>
+  <si>
+    <t>G584V</t>
+  </si>
+  <si>
+    <t>W585C</t>
+  </si>
+  <si>
+    <t>L589P</t>
+  </si>
+  <si>
+    <t>I593T</t>
+  </si>
+  <si>
+    <t>I593M</t>
+  </si>
+  <si>
+    <t>P596T</t>
+  </si>
+  <si>
+    <t>P596S</t>
+  </si>
+  <si>
+    <t>Y597H</t>
+  </si>
+  <si>
+    <t>G603S</t>
+  </si>
+  <si>
+    <t>P605L</t>
+  </si>
+  <si>
+    <t>S606F</t>
+  </si>
+  <si>
+    <t>D609N</t>
+  </si>
+  <si>
+    <t>Y611F</t>
+  </si>
+  <si>
+    <t>Y616F</t>
+  </si>
+  <si>
+    <t>S621C</t>
+  </si>
+  <si>
+    <t>S621N</t>
+  </si>
+  <si>
+    <t>L622F</t>
+  </si>
+  <si>
+    <t>T623S</t>
+  </si>
+  <si>
+    <t>V625M</t>
+  </si>
+  <si>
+    <t>G626R</t>
+  </si>
+  <si>
+    <t>G626S</t>
+  </si>
+  <si>
+    <t>N633T</t>
+  </si>
+  <si>
+    <t>T634A</t>
+  </si>
+  <si>
+    <t>N635D</t>
+  </si>
+  <si>
+    <t>I639F</t>
+  </si>
+  <si>
+    <t>F640V</t>
+  </si>
+  <si>
+    <t>I642V</t>
+  </si>
+  <si>
+    <t>I642L</t>
+  </si>
+  <si>
+    <t>M645V</t>
+  </si>
+  <si>
+    <t>M646I</t>
+  </si>
+  <si>
+    <t>G648A</t>
+  </si>
+  <si>
+    <t>I655F</t>
+  </si>
+  <si>
+    <t>L693P</t>
+  </si>
+  <si>
+    <t>R696C</t>
+  </si>
+  <si>
+    <t>E698K</t>
+  </si>
+  <si>
+    <t>I711V</t>
+  </si>
+  <si>
+    <t>L717P</t>
+  </si>
+  <si>
+    <t>R744Q</t>
+  </si>
+  <si>
+    <t>R744P</t>
+  </si>
+  <si>
+    <t>D774A</t>
+  </si>
+  <si>
+    <t>L776P</t>
+  </si>
+  <si>
+    <t>R784W</t>
+  </si>
+  <si>
+    <t>R784Q</t>
+  </si>
+  <si>
+    <t>E788K</t>
+  </si>
+  <si>
+    <t>R791W</t>
+  </si>
+  <si>
+    <t>R791Q</t>
+  </si>
+  <si>
+    <t>G806R</t>
+  </si>
+  <si>
+    <t>K817E</t>
+  </si>
+  <si>
+    <t>S818L</t>
+  </si>
+  <si>
+    <t>N819K</t>
+  </si>
+  <si>
+    <t>G820R</t>
+  </si>
+  <si>
+    <t>V822L</t>
+  </si>
+  <si>
+    <t>V822M</t>
+  </si>
+  <si>
+    <t>V822G</t>
+  </si>
+  <si>
+    <t>R823Q</t>
+  </si>
+  <si>
+    <t>R823P</t>
+  </si>
+  <si>
+    <t>C828G</t>
+  </si>
+  <si>
+    <t>H831P</t>
+  </si>
+  <si>
+    <t>R835W</t>
+  </si>
+  <si>
+    <t>D837H</t>
+  </si>
+  <si>
+    <t>D837N</t>
+  </si>
+  <si>
+    <t>Y845N</t>
+  </si>
+  <si>
+    <t>P846L</t>
+  </si>
+  <si>
+    <t>R863Q</t>
+  </si>
+  <si>
+    <t>G628R</t>
+  </si>
   <si>
     <t>critère1</t>
   </si>
@@ -34,9 +488,294 @@
     <t>clash</t>
   </si>
   <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>[0, 0]</t>
+  </si>
+  <si>
+    <t>[3, 6, 1]</t>
+  </si>
+  <si>
+    <t>no rotamers</t>
+  </si>
+  <si>
+    <t>[0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>[13, 0]</t>
+  </si>
+  <si>
+    <t>[0, 0, 1]</t>
+  </si>
+  <si>
+    <t>[4, 0]</t>
+  </si>
+  <si>
+    <t>[20, 28, 27]</t>
+  </si>
+  <si>
+    <t>[7, 35]</t>
+  </si>
+  <si>
+    <t>[10]</t>
+  </si>
+  <si>
+    <t>[5, 26, 6, 9]</t>
+  </si>
+  <si>
+    <t>[1, 0]</t>
+  </si>
+  <si>
+    <t>[0, 11]</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>[6, 57, 11]</t>
+  </si>
+  <si>
+    <t>[2, 0, 0]</t>
+  </si>
+  <si>
+    <t>[2, 0]</t>
+  </si>
+  <si>
+    <t>[10, 21, 15]</t>
+  </si>
+  <si>
+    <t>[0, 4, 2]</t>
+  </si>
+  <si>
+    <t>[1, 4]</t>
+  </si>
+  <si>
+    <t>[30]</t>
+  </si>
+  <si>
+    <t>[1, 0, 0]</t>
+  </si>
+  <si>
+    <t>[4, 21, 15]</t>
+  </si>
+  <si>
+    <t>[0, 4]</t>
+  </si>
+  <si>
+    <t>[0, 17]</t>
+  </si>
+  <si>
+    <t>[3, 7]</t>
+  </si>
+  <si>
+    <t>[13, 54]</t>
+  </si>
+  <si>
+    <t>[3, 5]</t>
+  </si>
+  <si>
+    <t>[0, 5]</t>
+  </si>
+  <si>
+    <t>[3, 0, 5]</t>
+  </si>
+  <si>
+    <t>[1, 0, 1]</t>
+  </si>
+  <si>
+    <t>[0, 20, 0]</t>
+  </si>
+  <si>
+    <t>[3, 6]</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>[0, 1, 0]</t>
+  </si>
+  <si>
+    <t>[7, 3]</t>
+  </si>
+  <si>
+    <t>[10, 17]</t>
+  </si>
+  <si>
+    <t>[0, 3]</t>
+  </si>
+  <si>
+    <t>[8, 7]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[13, 2, 21, 4, 21]</t>
+  </si>
+  <si>
+    <t>[22, 2, 30]</t>
+  </si>
+  <si>
+    <t>[3, 8, 5]</t>
+  </si>
+  <si>
+    <t>[18, 36, 34]</t>
+  </si>
+  <si>
+    <t>[1, 17, 0]</t>
+  </si>
+  <si>
+    <t>[0, 2, 0]</t>
+  </si>
+  <si>
+    <t>[0, 1, 1]</t>
+  </si>
+  <si>
+    <t>[10, 10, 11]</t>
+  </si>
+  <si>
+    <t>[1, 3]</t>
+  </si>
+  <si>
+    <t>[2, 5]</t>
+  </si>
+  <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[1, 54, 49]</t>
+  </si>
+  <si>
+    <t>[1, 27, 27]</t>
+  </si>
+  <si>
+    <t>[13, 0, 21, 50, 1]</t>
+  </si>
+  <si>
+    <t>[4, 11, 12]</t>
+  </si>
+  <si>
+    <t>[33]</t>
+  </si>
+  <si>
+    <t>[0, 2]</t>
+  </si>
+  <si>
+    <t>[5]</t>
+  </si>
+  <si>
+    <t>[3, 18]</t>
+  </si>
+  <si>
+    <t>[24, 38, 21]</t>
+  </si>
+  <si>
+    <t>[4, 18]</t>
+  </si>
+  <si>
+    <t>[3, 2, 0, 7, 0]</t>
+  </si>
+  <si>
+    <t>[5, 1, 0]</t>
+  </si>
+  <si>
+    <t>[4, 33, 33, 31]</t>
+  </si>
+  <si>
+    <t>[18]</t>
+  </si>
+  <si>
+    <t>[2, 5, 1]</t>
+  </si>
+  <si>
+    <t>[11, 9]</t>
+  </si>
+  <si>
     <t>minimisation</t>
   </si>
   <si>
+    <t>[2, 2, 0]</t>
+  </si>
+  <si>
+    <t>[10, 0]</t>
+  </si>
+  <si>
+    <t>[6, 7, 16]</t>
+  </si>
+  <si>
+    <t>[9]</t>
+  </si>
+  <si>
+    <t>[0, 3, 0, 1]</t>
+  </si>
+  <si>
+    <t>[2, 21, 3]</t>
+  </si>
+  <si>
+    <t>[3, 5, 3]</t>
+  </si>
+  <si>
+    <t>[19]</t>
+  </si>
+  <si>
+    <t>[3, 29]</t>
+  </si>
+  <si>
+    <t>[0, 4, 0]</t>
+  </si>
+  <si>
+    <t>[1, 1]</t>
+  </si>
+  <si>
+    <t>[2, 3]</t>
+  </si>
+  <si>
+    <t>[0, 1, 0, 1, 12]</t>
+  </si>
+  <si>
+    <t>[3, 0, 9]</t>
+  </si>
+  <si>
+    <t>[3, 3, 3]</t>
+  </si>
+  <si>
+    <t>[2, 1, 2]</t>
+  </si>
+  <si>
+    <t>[3, 2, 2]</t>
+  </si>
+  <si>
+    <t>[0, 19, 21]</t>
+  </si>
+  <si>
+    <t>[1, 5, 7]</t>
+  </si>
+  <si>
+    <t>[3, 0, 8, 28, 0]</t>
+  </si>
+  <si>
+    <t>[3, 2, 1]</t>
+  </si>
+  <si>
+    <t>[23]</t>
+  </si>
+  <si>
+    <t>[11, 3, 2]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[4, 1, 0]</t>
+  </si>
+  <si>
+    <t>[0, 4, 5, 11]</t>
+  </si>
+  <si>
     <t>critère4</t>
   </si>
   <si>
@@ -44,6 +783,750 @@
   </si>
   <si>
     <t>AA_important en contact</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[15]</t>
+  </si>
+  <si>
+    <t>[124, 19]</t>
+  </si>
+  <si>
+    <t>[26, 20]</t>
+  </si>
+  <si>
+    <t>[26]</t>
+  </si>
+  <si>
+    <t>[32, 30, 42, 43, 41]</t>
+  </si>
+  <si>
+    <t>[56, 59, 49, 54, 45, 43, 30]</t>
+  </si>
+  <si>
+    <t>[49, 19, 47, 44, 29, 43]</t>
+  </si>
+  <si>
+    <t>[56, 55, 54, 44, 45, 51, 53]</t>
+  </si>
+  <si>
+    <t>[54, 51, 99, 98, 69, 68, 100, 101, 106]</t>
+  </si>
+  <si>
+    <t>[49, 100, 101]</t>
+  </si>
+  <si>
+    <t>[56, 54, 101]</t>
+  </si>
+  <si>
+    <t>[32, 66, 41]</t>
+  </si>
+  <si>
+    <t>[64, 66]</t>
+  </si>
+  <si>
+    <t>[59, 54, 30, 41, 64, 65, 70, 68, 69]</t>
+  </si>
+  <si>
+    <t>[69, 70]</t>
+  </si>
+  <si>
+    <t>[54, 70]</t>
+  </si>
+  <si>
+    <t>[74]</t>
+  </si>
+  <si>
+    <t>[70, 82, 80, 96]</t>
+  </si>
+  <si>
+    <t>[78, 79, 85]</t>
+  </si>
+  <si>
+    <t>[70, 98, 80, 96, 86, 79, 85]</t>
+  </si>
+  <si>
+    <t>[92, 87]</t>
+  </si>
+  <si>
+    <t>[111]</t>
+  </si>
+  <si>
+    <t>[98, 108]</t>
+  </si>
+  <si>
+    <t>[98, 71, 69, 100]</t>
+  </si>
+  <si>
+    <t>[58, 55, 54, 53, 100]</t>
+  </si>
+  <si>
+    <t>[124]</t>
+  </si>
+  <si>
+    <t>[114, 15, 32]</t>
+  </si>
+  <si>
+    <t>[51, 28, 108]</t>
+  </si>
+  <si>
+    <t>[108, 106]</t>
+  </si>
+  <si>
+    <t>[473, 474, 475]</t>
+  </si>
+  <si>
+    <t>[412, 413]</t>
+  </si>
+  <si>
+    <t>[410]</t>
+  </si>
+  <si>
+    <t>[422]</t>
+  </si>
+  <si>
+    <t>[463, 531, 528, 420]</t>
+  </si>
+  <si>
+    <t>[559, 563, 421, 420]</t>
+  </si>
+  <si>
+    <t>[562, 611]</t>
+  </si>
+  <si>
+    <t>[534, 531]</t>
+  </si>
+  <si>
+    <t>[483, 474]</t>
+  </si>
+  <si>
+    <t>[402, 475]</t>
+  </si>
+  <si>
+    <t>[488, 474, 475]</t>
+  </si>
+  <si>
+    <t>[470]</t>
+  </si>
+  <si>
+    <t>[528]</t>
+  </si>
+  <si>
+    <t>[531, 421, 422]</t>
+  </si>
+  <si>
+    <t>[531]</t>
+  </si>
+  <si>
+    <t>[463, 534, 421, 528]</t>
+  </si>
+  <si>
+    <t>[537, 535, 531, 501]</t>
+  </si>
+  <si>
+    <t>[552]</t>
+  </si>
+  <si>
+    <t>[555, 554]</t>
+  </si>
+  <si>
+    <t>[554]</t>
+  </si>
+  <si>
+    <t>[558, 555, 551, 552]</t>
+  </si>
+  <si>
+    <t>[622, 618, 559, 558, 563, 564, 565, 562]</t>
+  </si>
+  <si>
+    <t>[622, 618, 558, 563, 564, 565, 615, 562]</t>
+  </si>
+  <si>
+    <t>[568, 622, 618, 561, 562, 640, 644]</t>
+  </si>
+  <si>
+    <t>[568, 618, 561, 562, 563, 565, 640]</t>
+  </si>
+  <si>
+    <t>[568, 618, 561, 562, 563, 614, 615]</t>
+  </si>
+  <si>
+    <t>[563, 562, 570, 430]</t>
+  </si>
+  <si>
+    <t>[568, 563, 571, 570, 564, 640]</t>
+  </si>
+  <si>
+    <t>[618, 585, 572, 571, 564, 617, 565, 640]</t>
+  </si>
+  <si>
+    <t>[585, 572, 571, 564, 565, 617, 640]</t>
+  </si>
+  <si>
+    <t>[585, 572, 571, 565, 566, 614]</t>
+  </si>
+  <si>
+    <t>[572, 571, 566]</t>
+  </si>
+  <si>
+    <t>[572, 575]</t>
+  </si>
+  <si>
+    <t>[584]</t>
+  </si>
+  <si>
+    <t>[585, 634, 637, 588]</t>
+  </si>
+  <si>
+    <t>[568, 631, 632, 637, 588]</t>
+  </si>
+  <si>
+    <t>[593, 585, 591, 588]</t>
+  </si>
+  <si>
+    <t>[595, 594]</t>
+  </si>
+  <si>
+    <t>[597]</t>
+  </si>
+  <si>
+    <t>[605, 604, 595, 596]</t>
+  </si>
+  <si>
+    <t>[604]</t>
+  </si>
+  <si>
+    <t>[610, 595]</t>
+  </si>
+  <si>
+    <t>[595, 610, 609]</t>
+  </si>
+  <si>
+    <t>[593, 613, 610, 611]</t>
+  </si>
+  <si>
+    <t>[562, 609, 614, 615, 566, 427]</t>
+  </si>
+  <si>
+    <t>[620, 627, 613, 617, 615]</t>
+  </si>
+  <si>
+    <t>[623, 618, 620, 617, 645, 644]</t>
+  </si>
+  <si>
+    <t>[623, 618, 620, 617, 644]</t>
+  </si>
+  <si>
+    <t>[618, 564, 621, 645, 644]</t>
+  </si>
+  <si>
+    <t>[621, 620, 625]</t>
+  </si>
+  <si>
+    <t>[623, 620, 627, 626]</t>
+  </si>
+  <si>
+    <t>[621, 620, 645, 625, 632, 617]</t>
+  </si>
+  <si>
+    <t>[620, 625]</t>
+  </si>
+  <si>
+    <t>[631, 584, 634, 637, 638]</t>
+  </si>
+  <si>
+    <t>[634, 638]</t>
+  </si>
+  <si>
+    <t>[635, 642]</t>
+  </si>
+  <si>
+    <t>[637, 638, 571, 641, 642, 644]</t>
+  </si>
+  <si>
+    <t>[638, 640]</t>
+  </si>
+  <si>
+    <t>[641, 642, 649]</t>
+  </si>
+  <si>
+    <t>[642, 644, 649]</t>
+  </si>
+  <si>
+    <t>[554, 553, 657, 651, 658]</t>
+  </si>
+  <si>
+    <t>[696]</t>
+  </si>
+  <si>
+    <t>[818, 835]</t>
+  </si>
+  <si>
+    <t>[783, 828]</t>
+  </si>
+  <si>
+    <t>[823, 822]</t>
+  </si>
+  <si>
+    <t>[818]</t>
+  </si>
+  <si>
+    <t>[833, 805]</t>
+  </si>
+  <si>
+    <t>[788]</t>
+  </si>
+  <si>
+    <t>[788, 805, 823]</t>
+  </si>
+  <si>
+    <t>[788, 823, 805]</t>
+  </si>
+  <si>
+    <t>[788, 822]</t>
+  </si>
+  <si>
+    <t>[837]</t>
+  </si>
+  <si>
+    <t>[835]</t>
+  </si>
+  <si>
+    <t>[846]</t>
+  </si>
+  <si>
+    <t>[627, 626]</t>
+  </si>
+  <si>
+    <t>nombre AA important</t>
+  </si>
+  <si>
+    <t>Q11H</t>
+  </si>
+  <si>
+    <t>L15N</t>
+  </si>
+  <si>
+    <t>I19F</t>
+  </si>
+  <si>
+    <t>I19N</t>
+  </si>
+  <si>
+    <t>R27H</t>
+  </si>
+  <si>
+    <t>N38K</t>
+  </si>
+  <si>
+    <t>Y43C</t>
+  </si>
+  <si>
+    <t>E50G</t>
+  </si>
+  <si>
+    <t>R56L</t>
+  </si>
+  <si>
+    <t>V59E</t>
+  </si>
+  <si>
+    <t>P72T</t>
+  </si>
+  <si>
+    <t>T74R</t>
+  </si>
+  <si>
+    <t>L87P</t>
+  </si>
+  <si>
+    <t>E91D</t>
+  </si>
+  <si>
+    <t>A97P</t>
+  </si>
+  <si>
+    <t>A97G</t>
+  </si>
+  <si>
+    <t>R100G</t>
+  </si>
+  <si>
+    <t>R100Q</t>
+  </si>
+  <si>
+    <t>C105G</t>
+  </si>
+  <si>
+    <t>V115M</t>
+  </si>
+  <si>
+    <t>L127F</t>
+  </si>
+  <si>
+    <t>W412R</t>
+  </si>
+  <si>
+    <t>A422D</t>
+  </si>
+  <si>
+    <t>M462T</t>
+  </si>
+  <si>
+    <t>H485Y</t>
+  </si>
+  <si>
+    <t>G487R</t>
+  </si>
+  <si>
+    <t>Y493C</t>
+  </si>
+  <si>
+    <t>D501N</t>
+  </si>
+  <si>
+    <t>R534L</t>
+  </si>
+  <si>
+    <t>A547V</t>
+  </si>
+  <si>
+    <t>A547T</t>
+  </si>
+  <si>
+    <t>C555Y</t>
+  </si>
+  <si>
+    <t>A561T</t>
+  </si>
+  <si>
+    <t>A565G</t>
+  </si>
+  <si>
+    <t>G572S</t>
+  </si>
+  <si>
+    <t>G572C</t>
+  </si>
+  <si>
+    <t>D591H</t>
+  </si>
+  <si>
+    <t>D591G</t>
+  </si>
+  <si>
+    <t>I593V</t>
+  </si>
+  <si>
+    <t>G604S</t>
+  </si>
+  <si>
+    <t>T613M</t>
+  </si>
+  <si>
+    <t>A614V</t>
+  </si>
+  <si>
+    <t>T618A</t>
+  </si>
+  <si>
+    <t>S620G</t>
+  </si>
+  <si>
+    <t>G628S</t>
+  </si>
+  <si>
+    <t>N629S</t>
+  </si>
+  <si>
+    <t>P632L</t>
+  </si>
+  <si>
+    <t>N633S</t>
+  </si>
+  <si>
+    <t>E637Q</t>
+  </si>
+  <si>
+    <t>S649P</t>
+  </si>
+  <si>
+    <t>G657R</t>
+  </si>
+  <si>
+    <t>N658S</t>
+  </si>
+  <si>
+    <t>S660L</t>
+  </si>
+  <si>
+    <t>D712N</t>
+  </si>
+  <si>
+    <t>P721L</t>
+  </si>
+  <si>
+    <t>L732P</t>
+  </si>
+  <si>
+    <t>R752W</t>
+  </si>
+  <si>
+    <t>P765L</t>
+  </si>
+  <si>
+    <t>H771R</t>
+  </si>
+  <si>
+    <t>S783P</t>
+  </si>
+  <si>
+    <t>V796L</t>
+  </si>
+  <si>
+    <t>G800R</t>
+  </si>
+  <si>
+    <t>P808L</t>
+  </si>
+  <si>
+    <t>R823W</t>
+  </si>
+  <si>
+    <t>C828Y</t>
+  </si>
+  <si>
+    <t>I833M</t>
+  </si>
+  <si>
+    <t>R835P</t>
+  </si>
+  <si>
+    <t>Y845D</t>
+  </si>
+  <si>
+    <t>P846A</t>
+  </si>
+  <si>
+    <t>[8, 14, 8]</t>
+  </si>
+  <si>
+    <t>[17, 6]</t>
+  </si>
+  <si>
+    <t>[3, 0]</t>
+  </si>
+  <si>
+    <t>[1, 5]</t>
+  </si>
+  <si>
+    <t>[24, 32, 38]</t>
+  </si>
+  <si>
+    <t>[6]</t>
+  </si>
+  <si>
+    <t>[0, 4, 7, 2]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 37]</t>
+  </si>
+  <si>
+    <t>[13, 24, 15]</t>
+  </si>
+  <si>
+    <t>[4, 3, 2]</t>
+  </si>
+  <si>
+    <t>[5, 6]</t>
+  </si>
+  <si>
+    <t>[0, 2, 1]</t>
+  </si>
+  <si>
+    <t>[0, 10, 0]</t>
+  </si>
+  <si>
+    <t>[18, 21]</t>
+  </si>
+  <si>
+    <t>[1, 25, 2]</t>
+  </si>
+  <si>
+    <t>[3, 8]</t>
+  </si>
+  <si>
+    <t>[0, 3, 1]</t>
+  </si>
+  <si>
+    <t>[4, 11]</t>
+  </si>
+  <si>
+    <t>[10, 22]</t>
+  </si>
+  <si>
+    <t>[2, 7]</t>
+  </si>
+  <si>
+    <t>[3, 2]</t>
+  </si>
+  <si>
+    <t>[11]</t>
+  </si>
+  <si>
+    <t>[15, 37, 39]</t>
+  </si>
+  <si>
+    <t>[1, 14, 1, 1]</t>
+  </si>
+  <si>
+    <t>[4, 4]</t>
+  </si>
+  <si>
+    <t>[1, 2, 1]</t>
+  </si>
+  <si>
+    <t>[20, 6, 17]</t>
+  </si>
+  <si>
+    <t>[0, 0, 1, 0]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 4]</t>
+  </si>
+  <si>
+    <t>[1, 3, 0]</t>
+  </si>
+  <si>
+    <t>[0, 7, 0]</t>
+  </si>
+  <si>
+    <t>[1, 2]</t>
+  </si>
+  <si>
+    <t>[5, 10, 11]</t>
+  </si>
+  <si>
+    <t>1.374620380162278</t>
+  </si>
+  <si>
+    <t>3.374620380162278</t>
+  </si>
+  <si>
+    <t>[19, 124]</t>
+  </si>
+  <si>
+    <t>[45, 15, 31, 43, 29]</t>
+  </si>
+  <si>
+    <t>[15, 31, 43, 29]</t>
+  </si>
+  <si>
+    <t>[45, 28, 29]</t>
+  </si>
+  <si>
+    <t>[31, 30, 42, 41, 44]</t>
+  </si>
+  <si>
+    <t>[59, 58, 55, 44]</t>
+  </si>
+  <si>
+    <t>[55, 54, 44, 56]</t>
+  </si>
+  <si>
+    <t>[99, 74]</t>
+  </si>
+  <si>
+    <t>[79, 99, 98, 72, 71, 70, 82, 69, 96]</t>
+  </si>
+  <si>
+    <t>[86, 85]</t>
+  </si>
+  <si>
+    <t>[111, 92]</t>
+  </si>
+  <si>
+    <t>[74, 106, 96]</t>
+  </si>
+  <si>
+    <t>[102, 106, 101, 51, 53]</t>
+  </si>
+  <si>
+    <t>[30, 29, 64, 111, 86]</t>
+  </si>
+  <si>
+    <t>[463, 410]</t>
+  </si>
+  <si>
+    <t>[488]</t>
+  </si>
+  <si>
+    <t>[537, 534]</t>
+  </si>
+  <si>
+    <t>[463, 537, 531, 501]</t>
+  </si>
+  <si>
+    <t>[551]</t>
+  </si>
+  <si>
+    <t>[559, 558, 551]</t>
+  </si>
+  <si>
+    <t>[585, 570, 575, 568]</t>
+  </si>
+  <si>
+    <t>[568, 585, 570, 575]</t>
+  </si>
+  <si>
+    <t>[588]</t>
+  </si>
+  <si>
+    <t>[605, 595, 597]</t>
+  </si>
+  <si>
+    <t>[593, 616, 609, 617]</t>
+  </si>
+  <si>
+    <t>[568, 618, 585, 613, 610, 611, 565, 617]</t>
+  </si>
+  <si>
+    <t>[627]</t>
+  </si>
+  <si>
+    <t>[630, 627, 616]</t>
+  </si>
+  <si>
+    <t>[568, 633, 634, 637, 638, 617, 641]</t>
+  </si>
+  <si>
+    <t>[584, 634, 637, 638]</t>
+  </si>
+  <si>
+    <t>[568, 632, 633, 634, 584, 617, 641, 640, 585]</t>
+  </si>
+  <si>
+    <t>[645]</t>
+  </si>
+  <si>
+    <t>[662, 553, 660]</t>
+  </si>
+  <si>
+    <t>[658]</t>
+  </si>
+  <si>
+    <t>[696, 818]</t>
+  </si>
+  <si>
+    <t>[784]</t>
+  </si>
+  <si>
+    <t>[696, 788, 822]</t>
+  </si>
+  <si>
+    <t>[784, 783]</t>
   </si>
 </sst>
 </file>
@@ -186,7 +1669,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,12 +1847,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,9 +2052,8 @@
     <xf numFmtId="0" fontId="16" fillId="28" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="84">
     <cellStyle name="20 % - Accent1 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
@@ -598,42 +2074,42 @@
     <cellStyle name="60 % - Accent1 5" xfId="57" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
     <cellStyle name="60 % - Accent1 6" xfId="64" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
     <cellStyle name="60 % - Accent1 7" xfId="71" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="60 % - Accent1 8" xfId="78" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="60 % - Accent1 8" xfId="78" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
     <cellStyle name="60 % - Accent2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="60 % - Accent2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="60 % - Accent2 4" xfId="51" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
     <cellStyle name="60 % - Accent2 5" xfId="58" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
     <cellStyle name="60 % - Accent2 6" xfId="65" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
     <cellStyle name="60 % - Accent2 7" xfId="72" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="60 % - Accent2 8" xfId="79" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="60 % - Accent2 8" xfId="79" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
     <cellStyle name="60 % - Accent3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="60 % - Accent3 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="60 % - Accent3 4" xfId="52" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
     <cellStyle name="60 % - Accent3 5" xfId="59" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="60 % - Accent3 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
     <cellStyle name="60 % - Accent3 7" xfId="73" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="60 % - Accent3 8" xfId="80" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="60 % - Accent3 8" xfId="80" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
     <cellStyle name="60 % - Accent4 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="60 % - Accent4 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="60 % - Accent4 4" xfId="53" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
     <cellStyle name="60 % - Accent4 5" xfId="60" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
     <cellStyle name="60 % - Accent4 6" xfId="67" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
     <cellStyle name="60 % - Accent4 7" xfId="74" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="60 % - Accent4 8" xfId="81" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="60 % - Accent4 8" xfId="81" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
     <cellStyle name="60 % - Accent5 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="60 % - Accent5 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
     <cellStyle name="60 % - Accent5 4" xfId="54" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
     <cellStyle name="60 % - Accent5 5" xfId="61" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
     <cellStyle name="60 % - Accent5 6" xfId="68" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
     <cellStyle name="60 % - Accent5 7" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="60 % - Accent5 8" xfId="82" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="60 % - Accent5 8" xfId="82" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
     <cellStyle name="60 % - Accent6 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="60 % - Accent6 3" xfId="48" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
     <cellStyle name="60 % - Accent6 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="60 % - Accent6 5" xfId="62" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
     <cellStyle name="60 % - Accent6 6" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="60 % - Accent6 7" xfId="76" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="60 % - Accent6 8" xfId="83" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="60 % - Accent6 8" xfId="83" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
     <cellStyle name="Accent1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="Accent2 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="Accent3 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
@@ -651,7 +2127,7 @@
     <cellStyle name="Neutre 5" xfId="56" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="Neutre 6" xfId="63" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
     <cellStyle name="Neutre 7" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Neutre 8" xfId="77" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Neutre 8" xfId="77" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
     <cellStyle name="Satisfaisant 2" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
@@ -975,67 +2451,7078 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BR9"/>
+  <dimension ref="A1:EV10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="D1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
-      <c r="BR1" s="1"/>
+    <row r="1" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>102</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>119</v>
+      </c>
+      <c r="DR1" t="s">
+        <v>120</v>
+      </c>
+      <c r="DS1" t="s">
+        <v>121</v>
+      </c>
+      <c r="DT1" t="s">
+        <v>122</v>
+      </c>
+      <c r="DU1" t="s">
+        <v>123</v>
+      </c>
+      <c r="DV1" t="s">
+        <v>124</v>
+      </c>
+      <c r="DW1" t="s">
+        <v>125</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>126</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>127</v>
+      </c>
+      <c r="DZ1" t="s">
+        <v>128</v>
+      </c>
+      <c r="EA1" t="s">
+        <v>129</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>130</v>
+      </c>
+      <c r="EC1" t="s">
+        <v>131</v>
+      </c>
+      <c r="ED1" t="s">
+        <v>132</v>
+      </c>
+      <c r="EE1" t="s">
+        <v>133</v>
+      </c>
+      <c r="EF1" t="s">
+        <v>134</v>
+      </c>
+      <c r="EG1" t="s">
+        <v>135</v>
+      </c>
+      <c r="EH1" t="s">
+        <v>136</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>137</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>138</v>
+      </c>
+      <c r="EK1" t="s">
+        <v>139</v>
+      </c>
+      <c r="EL1" t="s">
+        <v>140</v>
+      </c>
+      <c r="EM1" t="s">
+        <v>141</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>142</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>143</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>144</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>145</v>
+      </c>
+      <c r="ER1" t="s">
+        <v>146</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>147</v>
+      </c>
+      <c r="ET1" t="s">
+        <v>148</v>
+      </c>
+      <c r="EU1" t="s">
+        <v>149</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:152" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>1</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>1</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>1</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>1</v>
+      </c>
+      <c r="BM2">
+        <v>1</v>
+      </c>
+      <c r="BN2">
+        <v>1</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>1</v>
+      </c>
+      <c r="BQ2">
+        <v>1</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>0</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>0</v>
+      </c>
+      <c r="BX2">
+        <v>0</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CB2">
+        <v>2</v>
+      </c>
+      <c r="CC2">
+        <v>1</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
+      </c>
+      <c r="CE2">
+        <v>1</v>
+      </c>
+      <c r="CF2">
+        <v>0</v>
+      </c>
+      <c r="CG2">
+        <v>0</v>
+      </c>
+      <c r="CH2">
+        <v>0</v>
+      </c>
+      <c r="CI2">
+        <v>1</v>
+      </c>
+      <c r="CJ2">
+        <v>1</v>
+      </c>
+      <c r="CK2">
+        <v>2</v>
+      </c>
+      <c r="CL2">
+        <v>0</v>
+      </c>
+      <c r="CM2">
+        <v>0</v>
+      </c>
+      <c r="CN2">
+        <v>0</v>
+      </c>
+      <c r="CO2">
+        <v>0</v>
+      </c>
+      <c r="CP2">
+        <v>0</v>
+      </c>
+      <c r="CQ2">
+        <v>0</v>
+      </c>
+      <c r="CR2">
+        <v>1</v>
+      </c>
+      <c r="CS2">
+        <v>0</v>
+      </c>
+      <c r="CT2">
+        <v>1</v>
+      </c>
+      <c r="CU2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>0</v>
+      </c>
+      <c r="CW2">
+        <v>0</v>
+      </c>
+      <c r="CX2">
+        <v>0</v>
+      </c>
+      <c r="CY2">
+        <v>0</v>
+      </c>
+      <c r="CZ2">
+        <v>0</v>
+      </c>
+      <c r="DA2">
+        <v>0</v>
+      </c>
+      <c r="DB2">
+        <v>0</v>
+      </c>
+      <c r="DC2">
+        <v>2</v>
+      </c>
+      <c r="DD2">
+        <v>1</v>
+      </c>
+      <c r="DE2">
+        <v>0</v>
+      </c>
+      <c r="DF2">
+        <v>0</v>
+      </c>
+      <c r="DG2">
+        <v>0</v>
+      </c>
+      <c r="DH2">
+        <v>0</v>
+      </c>
+      <c r="DI2">
+        <v>0</v>
+      </c>
+      <c r="DJ2">
+        <v>0</v>
+      </c>
+      <c r="DK2">
+        <v>0</v>
+      </c>
+      <c r="DL2">
+        <v>0</v>
+      </c>
+      <c r="DM2">
+        <v>0</v>
+      </c>
+      <c r="DN2">
+        <v>0</v>
+      </c>
+      <c r="DO2">
+        <v>0</v>
+      </c>
+      <c r="DP2">
+        <v>0</v>
+      </c>
+      <c r="DQ2">
+        <v>1</v>
+      </c>
+      <c r="DR2">
+        <v>0</v>
+      </c>
+      <c r="DS2">
+        <v>0</v>
+      </c>
+      <c r="DT2">
+        <v>0</v>
+      </c>
+      <c r="DU2">
+        <v>0</v>
+      </c>
+      <c r="DV2">
+        <v>1</v>
+      </c>
+      <c r="DW2">
+        <v>0</v>
+      </c>
+      <c r="DX2">
+        <v>0</v>
+      </c>
+      <c r="DY2">
+        <v>0</v>
+      </c>
+      <c r="DZ2">
+        <v>0</v>
+      </c>
+      <c r="EA2">
+        <v>0</v>
+      </c>
+      <c r="EB2">
+        <v>0</v>
+      </c>
+      <c r="EC2">
+        <v>0</v>
+      </c>
+      <c r="ED2">
+        <v>2</v>
+      </c>
+      <c r="EE2">
+        <v>0</v>
+      </c>
+      <c r="EF2">
+        <v>1</v>
+      </c>
+      <c r="EG2">
+        <v>1</v>
+      </c>
+      <c r="EH2">
+        <v>2</v>
+      </c>
+      <c r="EI2">
+        <v>0</v>
+      </c>
+      <c r="EJ2">
+        <v>0</v>
+      </c>
+      <c r="EK2">
+        <v>1</v>
+      </c>
+      <c r="EL2">
+        <v>0</v>
+      </c>
+      <c r="EM2">
+        <v>1</v>
+      </c>
+      <c r="EN2">
+        <v>1</v>
+      </c>
+      <c r="EO2">
+        <v>0</v>
+      </c>
+      <c r="EP2">
+        <v>0</v>
+      </c>
+      <c r="EQ2">
+        <v>0</v>
+      </c>
+      <c r="ER2">
+        <v>0</v>
+      </c>
+      <c r="ES2">
+        <v>1</v>
+      </c>
+      <c r="ET2">
+        <v>0</v>
+      </c>
+      <c r="EU2">
+        <v>0</v>
+      </c>
+      <c r="EV2">
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>152</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>2</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>1</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>2</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>2</v>
+      </c>
+      <c r="BL3">
+        <v>2</v>
+      </c>
+      <c r="BM3">
+        <v>1</v>
+      </c>
+      <c r="BN3">
+        <v>2</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>1</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>1</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
+      <c r="CC3">
+        <v>0</v>
+      </c>
+      <c r="CD3">
+        <v>0</v>
+      </c>
+      <c r="CE3">
+        <v>1</v>
+      </c>
+      <c r="CF3">
+        <v>0</v>
+      </c>
+      <c r="CG3">
+        <v>0</v>
+      </c>
+      <c r="CH3">
+        <v>0</v>
+      </c>
+      <c r="CI3">
+        <v>0</v>
+      </c>
+      <c r="CJ3">
+        <v>0</v>
+      </c>
+      <c r="CK3">
+        <v>0</v>
+      </c>
+      <c r="CL3">
+        <v>0</v>
+      </c>
+      <c r="CM3">
+        <v>1</v>
+      </c>
+      <c r="CN3">
+        <v>0</v>
+      </c>
+      <c r="CO3">
+        <v>0</v>
+      </c>
+      <c r="CP3">
+        <v>0</v>
+      </c>
+      <c r="CQ3">
+        <v>0</v>
+      </c>
+      <c r="CR3">
+        <v>0</v>
+      </c>
+      <c r="CS3">
+        <v>0</v>
+      </c>
+      <c r="CT3">
+        <v>1</v>
+      </c>
+      <c r="CU3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>0</v>
+      </c>
+      <c r="CW3">
+        <v>0</v>
+      </c>
+      <c r="CX3">
+        <v>0</v>
+      </c>
+      <c r="CY3">
+        <v>0</v>
+      </c>
+      <c r="CZ3">
+        <v>0</v>
+      </c>
+      <c r="DA3">
+        <v>0</v>
+      </c>
+      <c r="DB3">
+        <v>0</v>
+      </c>
+      <c r="DC3">
+        <v>2</v>
+      </c>
+      <c r="DD3">
+        <v>0</v>
+      </c>
+      <c r="DE3">
+        <v>0</v>
+      </c>
+      <c r="DF3">
+        <v>0</v>
+      </c>
+      <c r="DG3">
+        <v>0</v>
+      </c>
+      <c r="DH3">
+        <v>0</v>
+      </c>
+      <c r="DI3">
+        <v>0</v>
+      </c>
+      <c r="DJ3">
+        <v>0</v>
+      </c>
+      <c r="DK3">
+        <v>0</v>
+      </c>
+      <c r="DL3">
+        <v>0</v>
+      </c>
+      <c r="DM3">
+        <v>0</v>
+      </c>
+      <c r="DN3">
+        <v>0</v>
+      </c>
+      <c r="DO3">
+        <v>0</v>
+      </c>
+      <c r="DP3">
+        <v>0</v>
+      </c>
+      <c r="DQ3">
+        <v>2</v>
+      </c>
+      <c r="DR3">
+        <v>0</v>
+      </c>
+      <c r="DS3">
+        <v>0</v>
+      </c>
+      <c r="DT3">
+        <v>0</v>
+      </c>
+      <c r="DU3">
+        <v>1</v>
+      </c>
+      <c r="DV3">
+        <v>2</v>
+      </c>
+      <c r="DW3">
+        <v>1</v>
+      </c>
+      <c r="DX3">
+        <v>0</v>
+      </c>
+      <c r="DY3">
+        <v>2</v>
+      </c>
+      <c r="DZ3">
+        <v>1</v>
+      </c>
+      <c r="EA3">
+        <v>0</v>
+      </c>
+      <c r="EB3">
+        <v>2</v>
+      </c>
+      <c r="EC3">
+        <v>1</v>
+      </c>
+      <c r="ED3">
+        <v>2</v>
+      </c>
+      <c r="EE3">
+        <v>0</v>
+      </c>
+      <c r="EF3">
+        <v>0</v>
+      </c>
+      <c r="EG3">
+        <v>0</v>
+      </c>
+      <c r="EH3">
+        <v>2</v>
+      </c>
+      <c r="EI3">
+        <v>0</v>
+      </c>
+      <c r="EJ3">
+        <v>0</v>
+      </c>
+      <c r="EK3">
+        <v>0</v>
+      </c>
+      <c r="EL3">
+        <v>1</v>
+      </c>
+      <c r="EM3">
+        <v>2</v>
+      </c>
+      <c r="EN3">
+        <v>0</v>
+      </c>
+      <c r="EO3">
+        <v>0</v>
+      </c>
+      <c r="EP3">
+        <v>2</v>
+      </c>
+      <c r="EQ3">
+        <v>0</v>
+      </c>
+      <c r="ER3">
+        <v>0</v>
+      </c>
+      <c r="ES3">
+        <v>0</v>
+      </c>
+      <c r="ET3">
+        <v>0</v>
+      </c>
+      <c r="EU3">
+        <v>1</v>
+      </c>
+      <c r="EV3">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>153</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>2</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>1</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>1</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>1</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>1</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>1</v>
+      </c>
+      <c r="BL4">
+        <v>1</v>
+      </c>
+      <c r="BM4">
+        <v>1</v>
+      </c>
+      <c r="BN4">
+        <v>1</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4">
+        <v>0</v>
+      </c>
+      <c r="CC4">
+        <v>0</v>
+      </c>
+      <c r="CD4">
+        <v>0</v>
+      </c>
+      <c r="CE4">
+        <v>1</v>
+      </c>
+      <c r="CF4">
+        <v>1</v>
+      </c>
+      <c r="CG4">
+        <v>0</v>
+      </c>
+      <c r="CH4">
+        <v>0</v>
+      </c>
+      <c r="CI4">
+        <v>0</v>
+      </c>
+      <c r="CJ4">
+        <v>0</v>
+      </c>
+      <c r="CK4">
+        <v>0</v>
+      </c>
+      <c r="CL4">
+        <v>0</v>
+      </c>
+      <c r="CM4">
+        <v>0</v>
+      </c>
+      <c r="CN4">
+        <v>0</v>
+      </c>
+      <c r="CO4">
+        <v>0</v>
+      </c>
+      <c r="CP4">
+        <v>0</v>
+      </c>
+      <c r="CQ4">
+        <v>1</v>
+      </c>
+      <c r="CR4">
+        <v>0</v>
+      </c>
+      <c r="CS4">
+        <v>0</v>
+      </c>
+      <c r="CT4">
+        <v>0</v>
+      </c>
+      <c r="CU4">
+        <v>1</v>
+      </c>
+      <c r="CV4">
+        <v>0</v>
+      </c>
+      <c r="CW4">
+        <v>0</v>
+      </c>
+      <c r="CX4">
+        <v>0</v>
+      </c>
+      <c r="CY4">
+        <v>0</v>
+      </c>
+      <c r="CZ4">
+        <v>0</v>
+      </c>
+      <c r="DA4">
+        <v>0</v>
+      </c>
+      <c r="DB4">
+        <v>0</v>
+      </c>
+      <c r="DC4">
+        <v>1</v>
+      </c>
+      <c r="DD4">
+        <v>0</v>
+      </c>
+      <c r="DE4">
+        <v>0</v>
+      </c>
+      <c r="DF4">
+        <v>0</v>
+      </c>
+      <c r="DG4">
+        <v>1</v>
+      </c>
+      <c r="DH4">
+        <v>0</v>
+      </c>
+      <c r="DI4">
+        <v>0</v>
+      </c>
+      <c r="DJ4">
+        <v>0</v>
+      </c>
+      <c r="DK4">
+        <v>0</v>
+      </c>
+      <c r="DL4">
+        <v>0</v>
+      </c>
+      <c r="DM4">
+        <v>0</v>
+      </c>
+      <c r="DN4">
+        <v>0</v>
+      </c>
+      <c r="DO4">
+        <v>0</v>
+      </c>
+      <c r="DP4">
+        <v>0</v>
+      </c>
+      <c r="DQ4">
+        <v>1</v>
+      </c>
+      <c r="DR4">
+        <v>2</v>
+      </c>
+      <c r="DS4">
+        <v>0</v>
+      </c>
+      <c r="DT4">
+        <v>0</v>
+      </c>
+      <c r="DU4">
+        <v>1</v>
+      </c>
+      <c r="DV4">
+        <v>1</v>
+      </c>
+      <c r="DW4">
+        <v>1</v>
+      </c>
+      <c r="DX4">
+        <v>0</v>
+      </c>
+      <c r="DY4">
+        <v>1</v>
+      </c>
+      <c r="DZ4">
+        <v>1</v>
+      </c>
+      <c r="EA4">
+        <v>2</v>
+      </c>
+      <c r="EB4">
+        <v>1</v>
+      </c>
+      <c r="EC4">
+        <v>1</v>
+      </c>
+      <c r="ED4">
+        <v>1</v>
+      </c>
+      <c r="EE4">
+        <v>2</v>
+      </c>
+      <c r="EF4">
+        <v>0</v>
+      </c>
+      <c r="EG4">
+        <v>1</v>
+      </c>
+      <c r="EH4">
+        <v>1</v>
+      </c>
+      <c r="EI4">
+        <v>0</v>
+      </c>
+      <c r="EJ4">
+        <v>0</v>
+      </c>
+      <c r="EK4">
+        <v>0</v>
+      </c>
+      <c r="EL4">
+        <v>1</v>
+      </c>
+      <c r="EM4">
+        <v>1</v>
+      </c>
+      <c r="EN4">
+        <v>0</v>
+      </c>
+      <c r="EO4">
+        <v>1</v>
+      </c>
+      <c r="EP4">
+        <v>1</v>
+      </c>
+      <c r="EQ4">
+        <v>2</v>
+      </c>
+      <c r="ER4">
+        <v>1</v>
+      </c>
+      <c r="ES4">
+        <v>0</v>
+      </c>
+      <c r="ET4">
+        <v>0</v>
+      </c>
+      <c r="EU4">
+        <v>1</v>
+      </c>
+      <c r="EV4">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:152" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K5" t="s">
+        <v>161</v>
+      </c>
+      <c r="L5" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N5" t="s">
+        <v>164</v>
+      </c>
+      <c r="O5" t="s">
+        <v>165</v>
+      </c>
+      <c r="P5" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>167</v>
+      </c>
+      <c r="R5" t="s">
+        <v>168</v>
+      </c>
+      <c r="S5" t="s">
+        <v>169</v>
+      </c>
+      <c r="T5" t="s">
+        <v>158</v>
+      </c>
+      <c r="U5" t="s">
+        <v>170</v>
+      </c>
+      <c r="V5" t="s">
+        <v>156</v>
+      </c>
+      <c r="W5" t="s">
+        <v>171</v>
+      </c>
+      <c r="X5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>176</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>179</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>180</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>181</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>182</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>173</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>173</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>159</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>159</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>158</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>184</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>185</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>186</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>184</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>155</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>188</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>189</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>190</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>191</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>192</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>173</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>156</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>156</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>158</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>193</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>156</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>159</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>194</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>168</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>195</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>156</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>196</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>160</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>156</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>197</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>159</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>155</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>159</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>159</v>
+      </c>
+      <c r="CV5" t="s">
+        <v>198</v>
+      </c>
+      <c r="CW5" t="s">
+        <v>159</v>
+      </c>
+      <c r="CX5" t="s">
+        <v>173</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>199</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>200</v>
+      </c>
+      <c r="DA5" t="s">
+        <v>156</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>201</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>178</v>
+      </c>
+      <c r="DD5" t="s">
+        <v>156</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>156</v>
+      </c>
+      <c r="DF5" t="s">
+        <v>158</v>
+      </c>
+      <c r="DG5" t="s">
+        <v>159</v>
+      </c>
+      <c r="DH5" t="s">
+        <v>202</v>
+      </c>
+      <c r="DI5" t="s">
+        <v>170</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>156</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>203</v>
+      </c>
+      <c r="DM5" t="s">
+        <v>190</v>
+      </c>
+      <c r="DN5" t="s">
+        <v>158</v>
+      </c>
+      <c r="DO5" t="s">
+        <v>204</v>
+      </c>
+      <c r="DP5" t="s">
+        <v>170</v>
+      </c>
+      <c r="DQ5" t="s">
+        <v>156</v>
+      </c>
+      <c r="DR5" t="s">
+        <v>190</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>190</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>205</v>
+      </c>
+      <c r="DU5" t="s">
+        <v>159</v>
+      </c>
+      <c r="DV5" t="s">
+        <v>206</v>
+      </c>
+      <c r="DW5" t="s">
+        <v>158</v>
+      </c>
+      <c r="DX5" t="s">
+        <v>207</v>
+      </c>
+      <c r="DY5" t="s">
+        <v>208</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>203</v>
+      </c>
+      <c r="EA5" t="s">
+        <v>209</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC5" t="s">
+        <v>211</v>
+      </c>
+      <c r="ED5" t="s">
+        <v>212</v>
+      </c>
+      <c r="EE5" t="s">
+        <v>213</v>
+      </c>
+      <c r="EF5" t="s">
+        <v>214</v>
+      </c>
+      <c r="EG5" t="s">
+        <v>215</v>
+      </c>
+      <c r="EH5" t="s">
+        <v>216</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>217</v>
+      </c>
+      <c r="EJ5" t="s">
+        <v>218</v>
+      </c>
+      <c r="EK5" t="s">
+        <v>158</v>
+      </c>
+      <c r="EL5" t="s">
+        <v>219</v>
+      </c>
+      <c r="EM5" t="s">
+        <v>207</v>
+      </c>
+      <c r="EN5" t="s">
+        <v>158</v>
+      </c>
+      <c r="EO5" t="s">
+        <v>170</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>220</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>221</v>
+      </c>
+      <c r="ER5" t="s">
+        <v>159</v>
+      </c>
+      <c r="ES5" t="s">
+        <v>222</v>
+      </c>
+      <c r="ET5" t="s">
+        <v>156</v>
+      </c>
+      <c r="EU5" t="s">
+        <v>223</v>
+      </c>
+      <c r="EV5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" t="s">
+        <v>158</v>
+      </c>
+      <c r="J6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K6" t="s">
+        <v>226</v>
+      </c>
+      <c r="L6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M6" t="s">
+        <v>163</v>
+      </c>
+      <c r="N6" t="s">
+        <v>227</v>
+      </c>
+      <c r="O6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P6" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>229</v>
+      </c>
+      <c r="R6" t="s">
+        <v>156</v>
+      </c>
+      <c r="S6" t="s">
+        <v>190</v>
+      </c>
+      <c r="T6" t="s">
+        <v>158</v>
+      </c>
+      <c r="U6" t="s">
+        <v>170</v>
+      </c>
+      <c r="V6" t="s">
+        <v>156</v>
+      </c>
+      <c r="W6" t="s">
+        <v>230</v>
+      </c>
+      <c r="X6" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>231</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>162</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>190</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>168</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>158</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>233</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>187</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>234</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>235</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>168</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>168</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>158</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>236</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>190</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>196</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>160</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>237</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>170</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>238</v>
+      </c>
+      <c r="CW6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CX6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>239</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>240</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>202</v>
+      </c>
+      <c r="DC6" t="s">
+        <v>159</v>
+      </c>
+      <c r="DD6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DF6" t="s">
+        <v>158</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>159</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>159</v>
+      </c>
+      <c r="DI6" t="s">
+        <v>160</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>159</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>158</v>
+      </c>
+      <c r="DO6" t="s">
+        <v>241</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>160</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DR6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DU6" t="s">
+        <v>159</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>156</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>158</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>170</v>
+      </c>
+      <c r="DY6" t="s">
+        <v>242</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>159</v>
+      </c>
+      <c r="EA6" t="s">
+        <v>243</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>244</v>
+      </c>
+      <c r="EC6" t="s">
+        <v>245</v>
+      </c>
+      <c r="ED6" t="s">
+        <v>246</v>
+      </c>
+      <c r="EE6" t="s">
+        <v>156</v>
+      </c>
+      <c r="EF6" t="s">
+        <v>155</v>
+      </c>
+      <c r="EG6" t="s">
+        <v>205</v>
+      </c>
+      <c r="EH6" t="s">
+        <v>247</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>190</v>
+      </c>
+      <c r="EJ6" t="s">
+        <v>248</v>
+      </c>
+      <c r="EK6" t="s">
+        <v>158</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>249</v>
+      </c>
+      <c r="EM6" t="s">
+        <v>160</v>
+      </c>
+      <c r="EN6" t="s">
+        <v>158</v>
+      </c>
+      <c r="EO6" t="s">
+        <v>160</v>
+      </c>
+      <c r="EP6" t="s">
+        <v>250</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>214</v>
+      </c>
+      <c r="ER6" t="s">
+        <v>159</v>
+      </c>
+      <c r="ES6" t="s">
+        <v>191</v>
+      </c>
+      <c r="ET6" t="s">
+        <v>156</v>
+      </c>
+      <c r="EU6" t="s">
+        <v>173</v>
+      </c>
+      <c r="EV6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>2</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>2</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>2</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>2</v>
+      </c>
+      <c r="AR7">
+        <v>2</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>2</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <v>1</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>1</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>2</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>2</v>
+      </c>
+      <c r="BL7">
+        <v>1</v>
+      </c>
+      <c r="BM7">
+        <v>1</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>2</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>1</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>1</v>
+      </c>
+      <c r="BU7">
+        <v>1</v>
+      </c>
+      <c r="BV7">
+        <v>1</v>
+      </c>
+      <c r="BW7">
+        <v>2</v>
+      </c>
+      <c r="BX7">
+        <v>1</v>
+      </c>
+      <c r="BY7">
+        <v>1</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>2</v>
+      </c>
+      <c r="CB7">
+        <v>2</v>
+      </c>
+      <c r="CC7">
+        <v>0</v>
+      </c>
+      <c r="CD7">
+        <v>0</v>
+      </c>
+      <c r="CE7">
+        <v>0</v>
+      </c>
+      <c r="CF7">
+        <v>2</v>
+      </c>
+      <c r="CG7">
+        <v>0</v>
+      </c>
+      <c r="CH7">
+        <v>0</v>
+      </c>
+      <c r="CI7">
+        <v>1</v>
+      </c>
+      <c r="CJ7">
+        <v>0</v>
+      </c>
+      <c r="CK7">
+        <v>1</v>
+      </c>
+      <c r="CL7">
+        <v>1</v>
+      </c>
+      <c r="CM7">
+        <v>0</v>
+      </c>
+      <c r="CN7">
+        <v>0</v>
+      </c>
+      <c r="CO7">
+        <v>0</v>
+      </c>
+      <c r="CP7">
+        <v>0</v>
+      </c>
+      <c r="CQ7">
+        <v>2</v>
+      </c>
+      <c r="CR7">
+        <v>0</v>
+      </c>
+      <c r="CS7">
+        <v>2</v>
+      </c>
+      <c r="CT7">
+        <v>0</v>
+      </c>
+      <c r="CU7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>2</v>
+      </c>
+      <c r="CW7">
+        <v>0</v>
+      </c>
+      <c r="CX7">
+        <v>1</v>
+      </c>
+      <c r="CY7">
+        <v>2</v>
+      </c>
+      <c r="CZ7">
+        <v>2</v>
+      </c>
+      <c r="DA7">
+        <v>0</v>
+      </c>
+      <c r="DB7">
+        <v>2</v>
+      </c>
+      <c r="DC7">
+        <v>1</v>
+      </c>
+      <c r="DD7">
+        <v>0</v>
+      </c>
+      <c r="DE7">
+        <v>0</v>
+      </c>
+      <c r="DF7">
+        <v>0</v>
+      </c>
+      <c r="DG7">
+        <v>0</v>
+      </c>
+      <c r="DH7">
+        <v>1</v>
+      </c>
+      <c r="DI7">
+        <v>1</v>
+      </c>
+      <c r="DJ7">
+        <v>0</v>
+      </c>
+      <c r="DK7">
+        <v>0</v>
+      </c>
+      <c r="DL7">
+        <v>1</v>
+      </c>
+      <c r="DM7">
+        <v>1</v>
+      </c>
+      <c r="DN7">
+        <v>0</v>
+      </c>
+      <c r="DO7">
+        <v>2</v>
+      </c>
+      <c r="DP7">
+        <v>1</v>
+      </c>
+      <c r="DQ7">
+        <v>0</v>
+      </c>
+      <c r="DR7">
+        <v>1</v>
+      </c>
+      <c r="DS7">
+        <v>1</v>
+      </c>
+      <c r="DT7">
+        <v>1</v>
+      </c>
+      <c r="DU7">
+        <v>0</v>
+      </c>
+      <c r="DV7">
+        <v>1</v>
+      </c>
+      <c r="DW7">
+        <v>0</v>
+      </c>
+      <c r="DX7">
+        <v>2</v>
+      </c>
+      <c r="DY7">
+        <v>2</v>
+      </c>
+      <c r="DZ7">
+        <v>1</v>
+      </c>
+      <c r="EA7">
+        <v>2</v>
+      </c>
+      <c r="EB7">
+        <v>2</v>
+      </c>
+      <c r="EC7">
+        <v>2</v>
+      </c>
+      <c r="ED7">
+        <v>2</v>
+      </c>
+      <c r="EE7">
+        <v>1</v>
+      </c>
+      <c r="EF7">
+        <v>2</v>
+      </c>
+      <c r="EG7">
+        <v>2</v>
+      </c>
+      <c r="EH7">
+        <v>2</v>
+      </c>
+      <c r="EI7">
+        <v>2</v>
+      </c>
+      <c r="EJ7">
+        <v>1</v>
+      </c>
+      <c r="EK7">
+        <v>0</v>
+      </c>
+      <c r="EL7">
+        <v>1.3746203801622781</v>
+      </c>
+      <c r="EM7">
+        <v>1</v>
+      </c>
+      <c r="EN7">
+        <v>0</v>
+      </c>
+      <c r="EO7">
+        <v>1</v>
+      </c>
+      <c r="EP7">
+        <v>2</v>
+      </c>
+      <c r="EQ7">
+        <v>2</v>
+      </c>
+      <c r="ER7">
+        <v>0</v>
+      </c>
+      <c r="ES7">
+        <v>2</v>
+      </c>
+      <c r="ET7">
+        <v>0</v>
+      </c>
+      <c r="EU7">
+        <v>2</v>
+      </c>
+      <c r="EV7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
         <v>3</v>
       </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>2</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>3</v>
+      </c>
+      <c r="AF8">
+        <v>4</v>
+      </c>
+      <c r="AG8">
+        <v>4</v>
+      </c>
+      <c r="AH8">
+        <v>2</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>3</v>
+      </c>
+      <c r="AM8">
+        <v>2</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>2</v>
+      </c>
+      <c r="AQ8">
+        <v>2</v>
+      </c>
+      <c r="AR8">
+        <v>3</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>3</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>2</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>2</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>1</v>
+      </c>
+      <c r="BC8">
+        <v>1</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>3</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>2</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>5</v>
+      </c>
+      <c r="BL8">
+        <v>5</v>
+      </c>
+      <c r="BM8">
+        <v>4</v>
+      </c>
+      <c r="BN8">
+        <v>4</v>
+      </c>
+      <c r="BO8">
+        <v>2</v>
+      </c>
+      <c r="BP8">
+        <v>1</v>
+      </c>
+      <c r="BQ8">
+        <v>1</v>
+      </c>
+      <c r="BR8">
+        <v>1</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>1</v>
+      </c>
+      <c r="BU8">
+        <v>1</v>
+      </c>
+      <c r="BV8">
+        <v>2</v>
+      </c>
+      <c r="BW8">
+        <v>2</v>
+      </c>
+      <c r="BX8">
+        <v>1</v>
+      </c>
+      <c r="BY8">
+        <v>1</v>
+      </c>
+      <c r="BZ8">
+        <v>1</v>
+      </c>
+      <c r="CA8">
+        <v>3</v>
+      </c>
+      <c r="CB8">
+        <v>4</v>
+      </c>
+      <c r="CC8">
+        <v>1</v>
+      </c>
+      <c r="CD8">
+        <v>0</v>
+      </c>
+      <c r="CE8">
+        <v>3</v>
+      </c>
+      <c r="CF8">
+        <v>3</v>
+      </c>
+      <c r="CG8">
+        <v>0</v>
+      </c>
+      <c r="CH8">
+        <v>0</v>
+      </c>
+      <c r="CI8">
+        <v>2</v>
+      </c>
+      <c r="CJ8">
+        <v>1</v>
+      </c>
+      <c r="CK8">
+        <v>3</v>
+      </c>
+      <c r="CL8">
+        <v>1</v>
+      </c>
+      <c r="CM8">
+        <v>1</v>
+      </c>
+      <c r="CN8">
+        <v>0</v>
+      </c>
+      <c r="CO8">
+        <v>0</v>
+      </c>
+      <c r="CP8">
+        <v>0</v>
+      </c>
+      <c r="CQ8">
+        <v>3</v>
+      </c>
+      <c r="CR8">
+        <v>1</v>
+      </c>
+      <c r="CS8">
+        <v>2</v>
+      </c>
+      <c r="CT8">
+        <v>2</v>
+      </c>
+      <c r="CU8">
+        <v>1</v>
+      </c>
+      <c r="CV8">
+        <v>2</v>
+      </c>
+      <c r="CW8">
+        <v>0</v>
+      </c>
+      <c r="CX8">
+        <v>1</v>
+      </c>
+      <c r="CY8">
+        <v>2</v>
+      </c>
+      <c r="CZ8">
+        <v>2</v>
+      </c>
+      <c r="DA8">
+        <v>0</v>
+      </c>
+      <c r="DB8">
+        <v>2</v>
+      </c>
+      <c r="DC8">
+        <v>6</v>
+      </c>
+      <c r="DD8">
+        <v>1</v>
+      </c>
+      <c r="DE8">
+        <v>0</v>
+      </c>
+      <c r="DF8">
+        <v>0</v>
+      </c>
+      <c r="DG8">
+        <v>1</v>
+      </c>
+      <c r="DH8">
+        <v>1</v>
+      </c>
+      <c r="DI8">
+        <v>1</v>
+      </c>
+      <c r="DJ8">
+        <v>0</v>
+      </c>
+      <c r="DK8">
+        <v>0</v>
+      </c>
+      <c r="DL8">
+        <v>1</v>
+      </c>
+      <c r="DM8">
+        <v>1</v>
+      </c>
+      <c r="DN8">
+        <v>0</v>
+      </c>
+      <c r="DO8">
+        <v>2</v>
+      </c>
+      <c r="DP8">
+        <v>1</v>
+      </c>
+      <c r="DQ8">
+        <v>4</v>
+      </c>
+      <c r="DR8">
+        <v>3</v>
+      </c>
+      <c r="DS8">
+        <v>1</v>
+      </c>
+      <c r="DT8">
+        <v>1</v>
+      </c>
+      <c r="DU8">
+        <v>2</v>
+      </c>
+      <c r="DV8">
+        <v>5</v>
+      </c>
+      <c r="DW8">
+        <v>2</v>
+      </c>
+      <c r="DX8">
+        <v>2</v>
+      </c>
+      <c r="DY8">
+        <v>5</v>
+      </c>
+      <c r="DZ8">
+        <v>3</v>
+      </c>
+      <c r="EA8">
+        <v>4</v>
+      </c>
+      <c r="EB8">
+        <v>5</v>
+      </c>
+      <c r="EC8">
+        <v>4</v>
+      </c>
+      <c r="ED8">
+        <v>7</v>
+      </c>
+      <c r="EE8">
+        <v>3</v>
+      </c>
+      <c r="EF8">
+        <v>3</v>
+      </c>
+      <c r="EG8">
+        <v>4</v>
+      </c>
+      <c r="EH8">
+        <v>7</v>
+      </c>
+      <c r="EI8">
+        <v>2</v>
+      </c>
+      <c r="EJ8">
+        <v>1</v>
+      </c>
+      <c r="EK8">
+        <v>1</v>
+      </c>
+      <c r="EL8">
+        <v>3.3746203801622778</v>
+      </c>
+      <c r="EM8">
+        <v>5</v>
+      </c>
+      <c r="EN8">
+        <v>1</v>
+      </c>
+      <c r="EO8">
+        <v>2</v>
+      </c>
+      <c r="EP8">
+        <v>5</v>
+      </c>
+      <c r="EQ8">
+        <v>4</v>
+      </c>
+      <c r="ER8">
+        <v>1</v>
+      </c>
+      <c r="ES8">
+        <v>3</v>
+      </c>
+      <c r="ET8">
+        <v>0</v>
+      </c>
+      <c r="EU8">
+        <v>4</v>
+      </c>
+      <c r="EV8">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" t="s">
+        <v>256</v>
+      </c>
+      <c r="F9" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" t="s">
+        <v>254</v>
+      </c>
+      <c r="H9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J9" t="s">
+        <v>257</v>
+      </c>
+      <c r="K9" t="s">
+        <v>258</v>
+      </c>
+      <c r="L9" t="s">
+        <v>259</v>
+      </c>
+      <c r="M9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" t="s">
+        <v>260</v>
+      </c>
+      <c r="O9" t="s">
+        <v>261</v>
+      </c>
+      <c r="P9" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>263</v>
+      </c>
+      <c r="R9" t="s">
+        <v>264</v>
+      </c>
+      <c r="S9" t="s">
+        <v>265</v>
+      </c>
+      <c r="T9" t="s">
+        <v>254</v>
+      </c>
+      <c r="U9" t="s">
+        <v>266</v>
+      </c>
+      <c r="V9" t="s">
+        <v>267</v>
+      </c>
+      <c r="W9" t="s">
+        <v>268</v>
+      </c>
+      <c r="X9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>270</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>272</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>273</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>274</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>275</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>276</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>277</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>278</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>279</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>280</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>281</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>282</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>283</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>285</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>286</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>286</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>287</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>289</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>290</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>291</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>292</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>293</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>294</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>295</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>296</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>297</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>298</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>299</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>300</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>301</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>302</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>303</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>304</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>305</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>306</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>307</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>308</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>309</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>310</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>311</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>312</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>313</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>314</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>315</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>254</v>
+      </c>
+      <c r="CF9" t="s">
+        <v>316</v>
+      </c>
+      <c r="CG9" t="s">
+        <v>317</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>254</v>
+      </c>
+      <c r="CI9" t="s">
+        <v>318</v>
+      </c>
+      <c r="CJ9" t="s">
+        <v>318</v>
+      </c>
+      <c r="CK9" t="s">
+        <v>319</v>
+      </c>
+      <c r="CL9" t="s">
+        <v>320</v>
+      </c>
+      <c r="CM9" t="s">
+        <v>321</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>321</v>
+      </c>
+      <c r="CO9" t="s">
+        <v>322</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>322</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>323</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>324</v>
+      </c>
+      <c r="CS9" t="s">
+        <v>325</v>
+      </c>
+      <c r="CT9" t="s">
+        <v>326</v>
+      </c>
+      <c r="CU9" t="s">
+        <v>327</v>
+      </c>
+      <c r="CV9" t="s">
+        <v>328</v>
+      </c>
+      <c r="CW9" t="s">
+        <v>329</v>
+      </c>
+      <c r="CX9" t="s">
+        <v>330</v>
+      </c>
+      <c r="CY9" t="s">
+        <v>331</v>
+      </c>
+      <c r="CZ9" t="s">
+        <v>332</v>
+      </c>
+      <c r="DA9" t="s">
+        <v>333</v>
+      </c>
+      <c r="DB9" t="s">
+        <v>334</v>
+      </c>
+      <c r="DC9" t="s">
+        <v>335</v>
+      </c>
+      <c r="DD9" t="s">
+        <v>336</v>
+      </c>
+      <c r="DE9" t="s">
+        <v>337</v>
+      </c>
+      <c r="DF9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DG9" t="s">
+        <v>338</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>339</v>
+      </c>
+      <c r="DI9" t="s">
+        <v>340</v>
+      </c>
+      <c r="DJ9" t="s">
+        <v>341</v>
+      </c>
+      <c r="DK9" t="s">
+        <v>341</v>
+      </c>
+      <c r="DL9" t="s">
+        <v>342</v>
+      </c>
+      <c r="DM9" t="s">
+        <v>343</v>
+      </c>
+      <c r="DN9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DO9" t="s">
+        <v>344</v>
+      </c>
+      <c r="DP9" t="s">
+        <v>345</v>
+      </c>
+      <c r="DQ9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DR9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DS9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DT9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DU9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DV9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DW9" t="s">
+        <v>254</v>
+      </c>
+      <c r="DX9" t="s">
+        <v>346</v>
+      </c>
+      <c r="DY9" t="s">
+        <v>347</v>
+      </c>
+      <c r="DZ9" t="s">
+        <v>347</v>
+      </c>
+      <c r="EA9" t="s">
+        <v>348</v>
+      </c>
+      <c r="EB9" t="s">
+        <v>349</v>
+      </c>
+      <c r="EC9" t="s">
+        <v>254</v>
+      </c>
+      <c r="ED9" t="s">
+        <v>350</v>
+      </c>
+      <c r="EE9" t="s">
+        <v>349</v>
+      </c>
+      <c r="EF9" t="s">
+        <v>254</v>
+      </c>
+      <c r="EG9" t="s">
+        <v>349</v>
+      </c>
+      <c r="EH9" t="s">
+        <v>351</v>
+      </c>
+      <c r="EI9" t="s">
+        <v>352</v>
+      </c>
+      <c r="EJ9" t="s">
+        <v>353</v>
+      </c>
+      <c r="EK9" t="s">
+        <v>254</v>
+      </c>
+      <c r="EL9" t="s">
+        <v>354</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>354</v>
+      </c>
+      <c r="EN9" t="s">
+        <v>254</v>
+      </c>
+      <c r="EO9" t="s">
+        <v>254</v>
+      </c>
+      <c r="EP9" t="s">
+        <v>355</v>
+      </c>
+      <c r="EQ9" t="s">
+        <v>356</v>
+      </c>
+      <c r="ER9" t="s">
+        <v>356</v>
+      </c>
+      <c r="ES9" t="s">
+        <v>357</v>
+      </c>
+      <c r="ET9" t="s">
+        <v>254</v>
+      </c>
+      <c r="EU9" t="s">
+        <v>349</v>
+      </c>
+      <c r="EV9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:152" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>7</v>
+      </c>
+      <c r="O10">
+        <v>6</v>
+      </c>
+      <c r="P10">
+        <v>7</v>
+      </c>
+      <c r="Q10">
+        <v>9</v>
+      </c>
+      <c r="R10">
+        <v>3</v>
+      </c>
+      <c r="S10">
+        <v>3</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
+      <c r="W10">
+        <v>9</v>
+      </c>
+      <c r="X10">
+        <v>2</v>
+      </c>
+      <c r="Y10">
+        <v>2</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>4</v>
+      </c>
+      <c r="AC10">
+        <v>3</v>
+      </c>
+      <c r="AD10">
+        <v>7</v>
+      </c>
+      <c r="AE10">
+        <v>2</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>2</v>
+      </c>
+      <c r="AK10">
+        <v>4</v>
+      </c>
+      <c r="AL10">
+        <v>5</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>3</v>
+      </c>
+      <c r="AP10">
+        <v>3</v>
+      </c>
+      <c r="AQ10">
+        <v>2</v>
+      </c>
+      <c r="AR10">
+        <v>3</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>2</v>
+      </c>
+      <c r="AU10">
+        <v>1</v>
+      </c>
+      <c r="AV10">
+        <v>1</v>
+      </c>
+      <c r="AW10">
+        <v>1</v>
+      </c>
+      <c r="AX10">
+        <v>4</v>
+      </c>
+      <c r="AY10">
+        <v>4</v>
+      </c>
+      <c r="AZ10">
+        <v>2</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>2</v>
+      </c>
+      <c r="BC10">
+        <v>2</v>
+      </c>
+      <c r="BD10">
+        <v>2</v>
+      </c>
+      <c r="BE10">
+        <v>3</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>1</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>1</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>3</v>
+      </c>
+      <c r="BL10">
+        <v>1</v>
+      </c>
+      <c r="BM10">
+        <v>4</v>
+      </c>
+      <c r="BN10">
+        <v>4</v>
+      </c>
+      <c r="BO10">
+        <v>1</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>2</v>
+      </c>
+      <c r="BR10">
+        <v>1</v>
+      </c>
+      <c r="BS10">
+        <v>4</v>
+      </c>
+      <c r="BT10">
+        <v>8</v>
+      </c>
+      <c r="BU10">
+        <v>8</v>
+      </c>
+      <c r="BV10">
+        <v>7</v>
+      </c>
+      <c r="BW10">
+        <v>7</v>
+      </c>
+      <c r="BX10">
+        <v>7</v>
+      </c>
+      <c r="BY10">
+        <v>4</v>
+      </c>
+      <c r="BZ10">
+        <v>6</v>
+      </c>
+      <c r="CA10">
+        <v>8</v>
+      </c>
+      <c r="CB10">
+        <v>7</v>
+      </c>
+      <c r="CC10">
+        <v>6</v>
+      </c>
+      <c r="CD10">
+        <v>3</v>
+      </c>
+      <c r="CE10">
+        <v>0</v>
+      </c>
+      <c r="CF10">
+        <v>2</v>
+      </c>
+      <c r="CG10">
+        <v>1</v>
+      </c>
+      <c r="CH10">
+        <v>0</v>
+      </c>
+      <c r="CI10">
+        <v>4</v>
+      </c>
+      <c r="CJ10">
+        <v>4</v>
+      </c>
+      <c r="CK10">
+        <v>5</v>
+      </c>
+      <c r="CL10">
+        <v>4</v>
+      </c>
+      <c r="CM10">
+        <v>2</v>
+      </c>
+      <c r="CN10">
+        <v>2</v>
+      </c>
+      <c r="CO10">
+        <v>1</v>
+      </c>
+      <c r="CP10">
+        <v>1</v>
+      </c>
+      <c r="CQ10">
+        <v>4</v>
+      </c>
+      <c r="CR10">
+        <v>1</v>
+      </c>
+      <c r="CS10">
+        <v>2</v>
+      </c>
+      <c r="CT10">
+        <v>3</v>
+      </c>
+      <c r="CU10">
+        <v>4</v>
+      </c>
+      <c r="CV10">
+        <v>6</v>
+      </c>
+      <c r="CW10">
+        <v>5</v>
+      </c>
+      <c r="CX10">
+        <v>6</v>
+      </c>
+      <c r="CY10">
+        <v>5</v>
+      </c>
+      <c r="CZ10">
+        <v>5</v>
+      </c>
+      <c r="DA10">
+        <v>3</v>
+      </c>
+      <c r="DB10">
+        <v>4</v>
+      </c>
+      <c r="DC10">
+        <v>6</v>
+      </c>
+      <c r="DD10">
+        <v>2</v>
+      </c>
+      <c r="DE10">
+        <v>5</v>
+      </c>
+      <c r="DF10">
+        <v>0</v>
+      </c>
+      <c r="DG10">
+        <v>2</v>
+      </c>
+      <c r="DH10">
+        <v>2</v>
+      </c>
+      <c r="DI10">
+        <v>6</v>
+      </c>
+      <c r="DJ10">
+        <v>2</v>
+      </c>
+      <c r="DK10">
+        <v>2</v>
+      </c>
+      <c r="DL10">
+        <v>3</v>
+      </c>
+      <c r="DM10">
+        <v>3</v>
+      </c>
+      <c r="DN10">
+        <v>0</v>
+      </c>
+      <c r="DO10">
+        <v>5</v>
+      </c>
+      <c r="DP10">
+        <v>1</v>
+      </c>
+      <c r="DQ10">
+        <v>0</v>
+      </c>
+      <c r="DR10">
+        <v>0</v>
+      </c>
+      <c r="DS10">
+        <v>0</v>
+      </c>
+      <c r="DT10">
+        <v>0</v>
+      </c>
+      <c r="DU10">
+        <v>0</v>
+      </c>
+      <c r="DV10">
+        <v>0</v>
+      </c>
+      <c r="DW10">
+        <v>0</v>
+      </c>
+      <c r="DX10">
+        <v>2</v>
+      </c>
+      <c r="DY10">
+        <v>2</v>
+      </c>
+      <c r="DZ10">
+        <v>2</v>
+      </c>
+      <c r="EA10">
+        <v>2</v>
+      </c>
+      <c r="EB10">
+        <v>1</v>
+      </c>
+      <c r="EC10">
+        <v>0</v>
+      </c>
+      <c r="ED10">
+        <v>2</v>
+      </c>
+      <c r="EE10">
+        <v>1</v>
+      </c>
+      <c r="EF10">
+        <v>0</v>
+      </c>
+      <c r="EG10">
+        <v>1</v>
+      </c>
+      <c r="EH10">
+        <v>1</v>
+      </c>
+      <c r="EI10">
+        <v>3</v>
+      </c>
+      <c r="EJ10">
+        <v>3</v>
+      </c>
+      <c r="EK10">
+        <v>0</v>
+      </c>
+      <c r="EL10">
+        <v>2</v>
+      </c>
+      <c r="EM10">
+        <v>2</v>
+      </c>
+      <c r="EN10">
+        <v>0</v>
+      </c>
+      <c r="EO10">
+        <v>0</v>
+      </c>
+      <c r="EP10">
+        <v>1</v>
+      </c>
+      <c r="EQ10">
+        <v>1</v>
+      </c>
+      <c r="ER10">
+        <v>1</v>
+      </c>
+      <c r="ES10">
+        <v>1</v>
+      </c>
+      <c r="ET10">
+        <v>0</v>
+      </c>
+      <c r="EU10">
+        <v>1</v>
+      </c>
+      <c r="EV10">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:CD10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J1" t="s">
+        <v>369</v>
+      </c>
+      <c r="K1" t="s">
+        <v>370</v>
+      </c>
+      <c r="L1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" t="s">
+        <v>371</v>
+      </c>
+      <c r="N1" t="s">
+        <v>372</v>
+      </c>
+      <c r="O1" t="s">
+        <v>373</v>
+      </c>
+      <c r="P1" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>375</v>
+      </c>
+      <c r="R1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" t="s">
+        <v>376</v>
+      </c>
+      <c r="T1" t="s">
+        <v>377</v>
+      </c>
+      <c r="U1" t="s">
+        <v>378</v>
+      </c>
+      <c r="V1" t="s">
+        <v>379</v>
+      </c>
+      <c r="W1" t="s">
+        <v>39</v>
+      </c>
+      <c r="X1" t="s">
+        <v>380</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>383</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>384</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>385</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>386</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>387</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>388</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>389</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>390</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>391</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>392</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>393</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>395</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>397</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>398</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>399</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>400</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>402</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>403</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>404</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>405</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>406</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>407</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>408</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>409</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>410</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>411</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>412</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>413</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>414</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>415</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>416</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>417</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>418</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>419</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>420</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>421</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>422</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>140</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>423</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>424</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>142</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>425</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>426</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>146</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>427</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>428</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>2</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+      <c r="BA2">
+        <v>1</v>
+      </c>
+      <c r="BB2">
+        <v>0</v>
+      </c>
+      <c r="BC2">
+        <v>0</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2">
+        <v>2</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>1</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0</v>
+      </c>
+      <c r="BP2">
+        <v>0</v>
+      </c>
+      <c r="BQ2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
+        <v>0</v>
+      </c>
+      <c r="BS2">
+        <v>2</v>
+      </c>
+      <c r="BT2">
+        <v>0</v>
+      </c>
+      <c r="BU2">
+        <v>0</v>
+      </c>
+      <c r="BV2">
+        <v>0</v>
+      </c>
+      <c r="BW2">
+        <v>1</v>
+      </c>
+      <c r="BX2">
+        <v>1</v>
+      </c>
+      <c r="BY2">
+        <v>0</v>
+      </c>
+      <c r="BZ2">
+        <v>1</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>0</v>
+      </c>
+      <c r="CD2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>2</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>2</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <v>2</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>1</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>2</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>2</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>1</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>2</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>1</v>
+      </c>
+      <c r="BV3">
+        <v>2</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>2</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
+      <c r="CC3">
+        <v>0</v>
+      </c>
+      <c r="CD3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>2</v>
+      </c>
+      <c r="AS4">
+        <v>1</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>1</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>1</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>1</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>1</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>2</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>1</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>1</v>
+      </c>
+      <c r="BV4">
+        <v>1</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>1</v>
+      </c>
+      <c r="CA4">
+        <v>1</v>
+      </c>
+      <c r="CB4">
+        <v>1</v>
+      </c>
+      <c r="CC4">
+        <v>0</v>
+      </c>
+      <c r="CD4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" t="s">
+        <v>431</v>
+      </c>
+      <c r="H5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I5" t="s">
+        <v>432</v>
+      </c>
+      <c r="J5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" t="s">
+        <v>190</v>
+      </c>
+      <c r="L5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M5" t="s">
+        <v>433</v>
+      </c>
+      <c r="N5" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" t="s">
+        <v>159</v>
+      </c>
+      <c r="P5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>158</v>
+      </c>
+      <c r="R5" t="s">
+        <v>156</v>
+      </c>
+      <c r="S5" t="s">
+        <v>158</v>
+      </c>
+      <c r="T5" t="s">
+        <v>434</v>
+      </c>
+      <c r="U5" t="s">
+        <v>158</v>
+      </c>
+      <c r="V5" t="s">
+        <v>435</v>
+      </c>
+      <c r="W5" t="s">
+        <v>160</v>
+      </c>
+      <c r="X5" t="s">
+        <v>436</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>236</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>437</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>438</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>439</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>440</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>441</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>155</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>158</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>159</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>442</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>159</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>443</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>444</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>207</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>191</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>156</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>445</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>160</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>446</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>447</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>448</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>159</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>449</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>209</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>173</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>160</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>235</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>219</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>450</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>451</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>452</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>453</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>159</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>225</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>158</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:82" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" t="s">
+        <v>158</v>
+      </c>
+      <c r="I6" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M6" t="s">
+        <v>455</v>
+      </c>
+      <c r="N6" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P6" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>158</v>
+      </c>
+      <c r="R6" t="s">
+        <v>156</v>
+      </c>
+      <c r="S6" t="s">
+        <v>158</v>
+      </c>
+      <c r="T6" t="s">
+        <v>155</v>
+      </c>
+      <c r="U6" t="s">
+        <v>158</v>
+      </c>
+      <c r="V6" t="s">
+        <v>456</v>
+      </c>
+      <c r="W6" t="s">
+        <v>160</v>
+      </c>
+      <c r="X6" t="s">
+        <v>457</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>213</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>458</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>158</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>236</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>459</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>235</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>460</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>235</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>159</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>243</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>168</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>156</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>249</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>170</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>461</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>196</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>159</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>158</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>0.18398431034006521</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1.5077745082278571</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0.65318336457988535</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.11467491073827429</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0.1024590000876635</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0.83819138230379719</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.2611893826767232</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0.61900465259108495</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>1.184022168236684</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>1.788734569402366</v>
+      </c>
+      <c r="AM7">
+        <v>0.88532508926172571</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1.7215796413193409</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0.4258645715615833</v>
+      </c>
+      <c r="AV7">
+        <v>0.33022360211339469</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>2</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>1.3125466656851099</v>
+      </c>
+      <c r="BF7">
+        <v>1</v>
+      </c>
+      <c r="BG7">
+        <v>1</v>
+      </c>
+      <c r="BH7">
+        <v>0.27982598543167109</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0.58785774864754281</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>2</v>
+      </c>
+      <c r="BM7">
+        <v>2</v>
+      </c>
+      <c r="BN7">
+        <v>2</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>1</v>
+      </c>
+      <c r="BQ7">
+        <v>2</v>
+      </c>
+      <c r="BR7">
+        <v>1.252399697096666</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>1</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>462</v>
+      </c>
+      <c r="BV7">
+        <v>2</v>
+      </c>
+      <c r="BW7">
+        <v>2</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>1</v>
+      </c>
+      <c r="BZ7">
+        <v>1</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7">
+        <v>0.80489953234823797</v>
+      </c>
+      <c r="CC7">
+        <v>0</v>
+      </c>
+      <c r="CD7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1.1839843103400649</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2.5077745082278571</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>1.653183364579885</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>0.11467491073827429</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0.1024590000876635</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
         <v>4</v>
       </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0.83819138230379719</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.2611893826767232</v>
+      </c>
+      <c r="Y8">
+        <v>4</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>2.6190046525910851</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>4.1840221682366838</v>
+      </c>
+      <c r="AH8">
+        <v>4</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>2.788734569402366</v>
+      </c>
+      <c r="AM8">
+        <v>0.88532508926172571</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>2</v>
+      </c>
+      <c r="AP8">
+        <v>2.7215796413193409</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>2</v>
+      </c>
+      <c r="AS8">
+        <v>3</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>1.425864571561583</v>
+      </c>
+      <c r="AV8">
+        <v>0.33022360211339469</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>2</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>2.3125466656851099</v>
+      </c>
+      <c r="BF8">
+        <v>1</v>
+      </c>
+      <c r="BG8">
+        <v>6</v>
+      </c>
+      <c r="BH8">
+        <v>0.27982598543167109</v>
+      </c>
+      <c r="BI8">
+        <v>1</v>
+      </c>
+      <c r="BJ8">
+        <v>1.5878577486475429</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>2</v>
+      </c>
+      <c r="BM8">
+        <v>5</v>
+      </c>
+      <c r="BN8">
+        <v>2</v>
+      </c>
+      <c r="BO8">
+        <v>1</v>
+      </c>
+      <c r="BP8">
+        <v>1</v>
+      </c>
+      <c r="BQ8">
+        <v>4</v>
+      </c>
+      <c r="BR8">
+        <v>1.252399697096666</v>
+      </c>
+      <c r="BS8">
+        <v>5</v>
+      </c>
+      <c r="BT8">
+        <v>1</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>463</v>
+      </c>
+      <c r="BV8">
+        <v>5</v>
+      </c>
+      <c r="BW8">
+        <v>3</v>
+      </c>
+      <c r="BX8">
+        <v>1</v>
+      </c>
+      <c r="BY8">
+        <v>1</v>
+      </c>
+      <c r="BZ8">
+        <v>5</v>
+      </c>
+      <c r="CA8">
+        <v>1</v>
+      </c>
+      <c r="CB8">
+        <v>2.8048995323482382</v>
+      </c>
+      <c r="CC8">
+        <v>0</v>
+      </c>
+      <c r="CD8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" t="s">
+        <v>464</v>
+      </c>
+      <c r="C9" t="s">
+        <v>465</v>
+      </c>
+      <c r="D9" t="s">
+        <v>466</v>
+      </c>
+      <c r="E9" t="s">
+        <v>467</v>
+      </c>
+      <c r="F9" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" t="s">
+        <v>468</v>
+      </c>
+      <c r="H9" t="s">
+        <v>254</v>
+      </c>
+      <c r="I9" t="s">
+        <v>469</v>
+      </c>
+      <c r="J9" t="s">
+        <v>470</v>
+      </c>
+      <c r="K9" t="s">
+        <v>471</v>
+      </c>
+      <c r="L9" t="s">
+        <v>271</v>
+      </c>
+      <c r="M9" t="s">
+        <v>472</v>
+      </c>
+      <c r="N9" t="s">
+        <v>473</v>
+      </c>
+      <c r="O9" t="s">
+        <v>474</v>
+      </c>
+      <c r="P9" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>254</v>
+      </c>
+      <c r="R9" t="s">
+        <v>278</v>
+      </c>
+      <c r="S9" t="s">
+        <v>254</v>
+      </c>
+      <c r="T9" t="s">
+        <v>476</v>
+      </c>
+      <c r="U9" t="s">
+        <v>254</v>
+      </c>
+      <c r="V9" t="s">
+        <v>280</v>
+      </c>
+      <c r="W9" t="s">
+        <v>281</v>
+      </c>
+      <c r="X9" t="s">
+        <v>477</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>478</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>479</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>295</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>480</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>481</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>300</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>482</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>482</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>302</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>483</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>306</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>484</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>485</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>318</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>486</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>321</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>487</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>488</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>489</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>329</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>490</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>491</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>492</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>493</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>494</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>495</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>496</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>497</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>498</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>499</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>348</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>354</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>500</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>501</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>355</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>356</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>357</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>254</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:82" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>9</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>4</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>5</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>3</v>
+      </c>
+      <c r="X10">
+        <v>5</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>4</v>
+      </c>
+      <c r="AB10">
+        <v>2</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>2</v>
+      </c>
+      <c r="AG10">
+        <v>4</v>
+      </c>
+      <c r="AH10">
+        <v>4</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>2</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
+      <c r="AM10">
+        <v>8</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>4</v>
+      </c>
+      <c r="AP10">
+        <v>4</v>
+      </c>
+      <c r="AQ10">
+        <v>4</v>
+      </c>
+      <c r="AR10">
+        <v>1</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>2</v>
+      </c>
+      <c r="AU10">
+        <v>3</v>
+      </c>
+      <c r="AV10">
+        <v>4</v>
+      </c>
+      <c r="AW10">
+        <v>8</v>
+      </c>
+      <c r="AX10">
+        <v>5</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>1</v>
+      </c>
+      <c r="BB10">
+        <v>3</v>
+      </c>
+      <c r="BC10">
         <v>7</v>
+      </c>
+      <c r="BD10">
+        <v>4</v>
+      </c>
+      <c r="BE10">
+        <v>9</v>
+      </c>
+      <c r="BF10">
+        <v>1</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>3</v>
+      </c>
+      <c r="BI10">
+        <v>1</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>2</v>
+      </c>
+      <c r="BP10">
+        <v>1</v>
+      </c>
+      <c r="BQ10">
+        <v>2</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>2</v>
+      </c>
+      <c r="BV10">
+        <v>3</v>
+      </c>
+      <c r="BW10">
+        <v>2</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>1</v>
+      </c>
+      <c r="CA10">
+        <v>1</v>
+      </c>
+      <c r="CB10">
+        <v>1</v>
+      </c>
+      <c r="CC10">
+        <v>0</v>
+      </c>
+      <c r="CD10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
